--- a/JsonConverter/ExcelFiles/PetActiveSkillData.xlsx
+++ b/JsonConverter/ExcelFiles/PetActiveSkillData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="80">
   <si>
     <t>아이디</t>
   </si>
@@ -164,6 +164,9 @@
     <t>Fire</t>
   </si>
   <si>
+    <t>FramePawn/ActiveEffect</t>
+  </si>
+  <si>
     <t>pet_skill_water_001</t>
   </si>
   <si>
@@ -174,6 +177,9 @@
   </si>
   <si>
     <t>Cold</t>
+  </si>
+  <si>
+    <t>WaterPawn/ActiveEffect</t>
   </si>
   <si>
     <t>pet_skill_earth_001</t>
@@ -191,6 +197,9 @@
     <t>Physical</t>
   </si>
   <si>
+    <t>EarthPawn/ActiveEffect</t>
+  </si>
+  <si>
     <t>pet_skill_air_001</t>
   </si>
   <si>
@@ -198,6 +207,9 @@
   </si>
   <si>
     <t>관통하지 않는 빠른 바람 투사체를 발사해 단일 적에게 물리 피해를 줍니다. 기본 공격 자체는 상태이상을 부여하지 않습니다.</t>
+  </si>
+  <si>
+    <t>WindPawn/ActiveEffect</t>
   </si>
   <si>
     <t>pet_skill_taunt</t>
@@ -234,6 +246,9 @@
   </si>
   <si>
     <t>Heal</t>
+  </si>
+  <si>
+    <t>WindBlass_Pet</t>
   </si>
   <si>
     <t>buff_windblessing</t>
@@ -351,11 +366,11 @@
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
@@ -831,24 +846,26 @@
       <c r="N4" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="O4" s="8"/>
+      <c r="O4" s="11" t="s">
+        <v>50</v>
+      </c>
       <c r="P4" s="8"/>
       <c r="Q4" s="8"/>
       <c r="R4" s="9"/>
       <c r="S4" s="9">
         <v>10.0</v>
       </c>
-      <c r="T4" s="11"/>
+      <c r="T4" s="12"/>
     </row>
     <row r="5" ht="33.75" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>46</v>
@@ -881,26 +898,28 @@
         <v>48</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="O5" s="8"/>
+        <v>54</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>55</v>
+      </c>
       <c r="P5" s="8"/>
       <c r="Q5" s="8"/>
       <c r="R5" s="9"/>
       <c r="S5" s="9">
         <v>10.0</v>
       </c>
-      <c r="T5" s="11"/>
+      <c r="T5" s="12"/>
     </row>
     <row r="6" ht="33.75" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>46</v>
@@ -921,32 +940,34 @@
       <c r="L6" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="M6" s="12" t="s">
-        <v>57</v>
+      <c r="M6" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="O6" s="8"/>
+        <v>60</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>61</v>
+      </c>
       <c r="P6" s="8"/>
       <c r="Q6" s="8"/>
       <c r="R6" s="9"/>
       <c r="S6" s="9">
         <v>2.5</v>
       </c>
-      <c r="T6" s="11">
+      <c r="T6" s="12">
         <v>2.0</v>
       </c>
     </row>
     <row r="7" ht="33.75" customHeight="1">
       <c r="A7" s="8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>46</v>
@@ -979,26 +1000,28 @@
         <v>48</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="O7" s="8"/>
+        <v>60</v>
+      </c>
+      <c r="O7" s="11" t="s">
+        <v>65</v>
+      </c>
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="9"/>
       <c r="S7" s="9">
         <v>11.0</v>
       </c>
-      <c r="T7" s="11"/>
+      <c r="T7" s="12"/>
     </row>
     <row r="8" ht="33.75" customHeight="1">
       <c r="A8" s="8" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>46</v>
@@ -1017,37 +1040,37 @@
       <c r="J8" s="8"/>
       <c r="K8" s="10"/>
       <c r="L8" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="M8" s="12" t="s">
-        <v>66</v>
+        <v>69</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="S8" s="9">
         <v>4.5</v>
       </c>
-      <c r="T8" s="11">
+      <c r="T8" s="12">
         <v>4.5</v>
       </c>
     </row>
     <row r="9" ht="33.75" customHeight="1">
       <c r="A9" s="8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E9" s="8">
         <v>15.0</v>
@@ -1063,24 +1086,26 @@
       <c r="J9" s="8"/>
       <c r="K9" s="10"/>
       <c r="L9" s="8" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="O9" s="8"/>
+        <v>77</v>
+      </c>
+      <c r="O9" s="11" t="s">
+        <v>78</v>
+      </c>
       <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
       <c r="R9" s="9" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="S9" s="9">
         <v>10.0</v>
       </c>
-      <c r="T9" s="11"/>
+      <c r="T9" s="12"/>
     </row>
     <row r="10">
       <c r="A10" s="8"/>
@@ -1102,7 +1127,7 @@
       <c r="Q10" s="8"/>
       <c r="R10" s="9"/>
       <c r="S10" s="9"/>
-      <c r="T10" s="11"/>
+      <c r="T10" s="12"/>
     </row>
     <row r="11">
       <c r="A11" s="8"/>
@@ -1124,7 +1149,7 @@
       <c r="Q11" s="8"/>
       <c r="R11" s="9"/>
       <c r="S11" s="9"/>
-      <c r="T11" s="11"/>
+      <c r="T11" s="12"/>
     </row>
     <row r="12">
       <c r="A12" s="8"/>
@@ -1146,7 +1171,7 @@
       <c r="Q12" s="8"/>
       <c r="R12" s="9"/>
       <c r="S12" s="9"/>
-      <c r="T12" s="11"/>
+      <c r="T12" s="12"/>
     </row>
     <row r="13">
       <c r="A13" s="8"/>
@@ -1168,7 +1193,7 @@
       <c r="Q13" s="8"/>
       <c r="R13" s="9"/>
       <c r="S13" s="9"/>
-      <c r="T13" s="11"/>
+      <c r="T13" s="12"/>
     </row>
     <row r="14">
       <c r="A14" s="8"/>
@@ -1190,7 +1215,7 @@
       <c r="Q14" s="8"/>
       <c r="R14" s="9"/>
       <c r="S14" s="9"/>
-      <c r="T14" s="11"/>
+      <c r="T14" s="12"/>
     </row>
     <row r="15">
       <c r="A15" s="8"/>
@@ -1212,7 +1237,7 @@
       <c r="Q15" s="8"/>
       <c r="R15" s="9"/>
       <c r="S15" s="9"/>
-      <c r="T15" s="11"/>
+      <c r="T15" s="12"/>
     </row>
     <row r="16">
       <c r="A16" s="8"/>
@@ -1234,7 +1259,7 @@
       <c r="Q16" s="8"/>
       <c r="R16" s="9"/>
       <c r="S16" s="9"/>
-      <c r="T16" s="11"/>
+      <c r="T16" s="12"/>
     </row>
     <row r="17">
       <c r="A17" s="8"/>
@@ -1256,7 +1281,7 @@
       <c r="Q17" s="8"/>
       <c r="R17" s="9"/>
       <c r="S17" s="9"/>
-      <c r="T17" s="11"/>
+      <c r="T17" s="12"/>
     </row>
     <row r="18">
       <c r="A18" s="8"/>
@@ -1278,7 +1303,7 @@
       <c r="Q18" s="8"/>
       <c r="R18" s="9"/>
       <c r="S18" s="9"/>
-      <c r="T18" s="11"/>
+      <c r="T18" s="12"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="8"/>
@@ -1300,7 +1325,7 @@
       <c r="Q19" s="8"/>
       <c r="R19" s="9"/>
       <c r="S19" s="9"/>
-      <c r="T19" s="11"/>
+      <c r="T19" s="12"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="8"/>
@@ -1322,7 +1347,7 @@
       <c r="Q20" s="8"/>
       <c r="R20" s="9"/>
       <c r="S20" s="9"/>
-      <c r="T20" s="11"/>
+      <c r="T20" s="12"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="8"/>
@@ -1344,7 +1369,7 @@
       <c r="Q21" s="8"/>
       <c r="R21" s="9"/>
       <c r="S21" s="9"/>
-      <c r="T21" s="11"/>
+      <c r="T21" s="12"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="8"/>
@@ -1366,7 +1391,7 @@
       <c r="Q22" s="8"/>
       <c r="R22" s="9"/>
       <c r="S22" s="9"/>
-      <c r="T22" s="11"/>
+      <c r="T22" s="12"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="8"/>
@@ -1388,7 +1413,7 @@
       <c r="Q23" s="8"/>
       <c r="R23" s="9"/>
       <c r="S23" s="9"/>
-      <c r="T23" s="11"/>
+      <c r="T23" s="12"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="8"/>
@@ -1410,7 +1435,7 @@
       <c r="Q24" s="8"/>
       <c r="R24" s="9"/>
       <c r="S24" s="9"/>
-      <c r="T24" s="11"/>
+      <c r="T24" s="12"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="8"/>
@@ -1432,7 +1457,7 @@
       <c r="Q25" s="8"/>
       <c r="R25" s="9"/>
       <c r="S25" s="9"/>
-      <c r="T25" s="11"/>
+      <c r="T25" s="12"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="8"/>
@@ -1454,7 +1479,7 @@
       <c r="Q26" s="8"/>
       <c r="R26" s="9"/>
       <c r="S26" s="9"/>
-      <c r="T26" s="11"/>
+      <c r="T26" s="12"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="8"/>
@@ -1476,7 +1501,7 @@
       <c r="Q27" s="8"/>
       <c r="R27" s="9"/>
       <c r="S27" s="9"/>
-      <c r="T27" s="11"/>
+      <c r="T27" s="12"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="8"/>
@@ -1498,7 +1523,7 @@
       <c r="Q28" s="8"/>
       <c r="R28" s="9"/>
       <c r="S28" s="9"/>
-      <c r="T28" s="11"/>
+      <c r="T28" s="12"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="8"/>
@@ -1520,7 +1545,7 @@
       <c r="Q29" s="8"/>
       <c r="R29" s="9"/>
       <c r="S29" s="9"/>
-      <c r="T29" s="11"/>
+      <c r="T29" s="12"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="8"/>
@@ -1542,7 +1567,7 @@
       <c r="Q30" s="8"/>
       <c r="R30" s="9"/>
       <c r="S30" s="9"/>
-      <c r="T30" s="11"/>
+      <c r="T30" s="12"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="8"/>
@@ -1564,7 +1589,7 @@
       <c r="Q31" s="8"/>
       <c r="R31" s="9"/>
       <c r="S31" s="9"/>
-      <c r="T31" s="11"/>
+      <c r="T31" s="12"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="8"/>
@@ -1586,7 +1611,7 @@
       <c r="Q32" s="8"/>
       <c r="R32" s="9"/>
       <c r="S32" s="9"/>
-      <c r="T32" s="11"/>
+      <c r="T32" s="12"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="8"/>
@@ -1608,7 +1633,7 @@
       <c r="Q33" s="8"/>
       <c r="R33" s="9"/>
       <c r="S33" s="9"/>
-      <c r="T33" s="11"/>
+      <c r="T33" s="12"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="8"/>
@@ -1630,7 +1655,7 @@
       <c r="Q34" s="8"/>
       <c r="R34" s="9"/>
       <c r="S34" s="9"/>
-      <c r="T34" s="11"/>
+      <c r="T34" s="12"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="8"/>
@@ -1652,7 +1677,7 @@
       <c r="Q35" s="8"/>
       <c r="R35" s="9"/>
       <c r="S35" s="9"/>
-      <c r="T35" s="11"/>
+      <c r="T35" s="12"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="8"/>
@@ -1674,7 +1699,7 @@
       <c r="Q36" s="8"/>
       <c r="R36" s="9"/>
       <c r="S36" s="9"/>
-      <c r="T36" s="11"/>
+      <c r="T36" s="12"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="8"/>
@@ -1696,7 +1721,7 @@
       <c r="Q37" s="8"/>
       <c r="R37" s="9"/>
       <c r="S37" s="9"/>
-      <c r="T37" s="11"/>
+      <c r="T37" s="12"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="8"/>
@@ -1718,7 +1743,7 @@
       <c r="Q38" s="8"/>
       <c r="R38" s="9"/>
       <c r="S38" s="9"/>
-      <c r="T38" s="11"/>
+      <c r="T38" s="12"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="8"/>
@@ -1740,7 +1765,7 @@
       <c r="Q39" s="8"/>
       <c r="R39" s="9"/>
       <c r="S39" s="9"/>
-      <c r="T39" s="11"/>
+      <c r="T39" s="12"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="8"/>
@@ -1762,7 +1787,7 @@
       <c r="Q40" s="8"/>
       <c r="R40" s="9"/>
       <c r="S40" s="9"/>
-      <c r="T40" s="11"/>
+      <c r="T40" s="12"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="8"/>
@@ -1784,7 +1809,7 @@
       <c r="Q41" s="8"/>
       <c r="R41" s="9"/>
       <c r="S41" s="9"/>
-      <c r="T41" s="11"/>
+      <c r="T41" s="12"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="8"/>
@@ -1806,7 +1831,7 @@
       <c r="Q42" s="8"/>
       <c r="R42" s="9"/>
       <c r="S42" s="9"/>
-      <c r="T42" s="11"/>
+      <c r="T42" s="12"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="8"/>
@@ -1828,7 +1853,7 @@
       <c r="Q43" s="8"/>
       <c r="R43" s="9"/>
       <c r="S43" s="9"/>
-      <c r="T43" s="11"/>
+      <c r="T43" s="12"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="8"/>
@@ -1850,7 +1875,7 @@
       <c r="Q44" s="8"/>
       <c r="R44" s="9"/>
       <c r="S44" s="9"/>
-      <c r="T44" s="11"/>
+      <c r="T44" s="12"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="8"/>
@@ -1872,7 +1897,7 @@
       <c r="Q45" s="8"/>
       <c r="R45" s="9"/>
       <c r="S45" s="9"/>
-      <c r="T45" s="11"/>
+      <c r="T45" s="12"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="8"/>
@@ -1894,7 +1919,7 @@
       <c r="Q46" s="8"/>
       <c r="R46" s="9"/>
       <c r="S46" s="9"/>
-      <c r="T46" s="11"/>
+      <c r="T46" s="12"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="8"/>
@@ -1916,7 +1941,7 @@
       <c r="Q47" s="8"/>
       <c r="R47" s="9"/>
       <c r="S47" s="9"/>
-      <c r="T47" s="11"/>
+      <c r="T47" s="12"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="8"/>
@@ -1938,7 +1963,7 @@
       <c r="Q48" s="8"/>
       <c r="R48" s="9"/>
       <c r="S48" s="9"/>
-      <c r="T48" s="11"/>
+      <c r="T48" s="12"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
@@ -1960,7 +1985,7 @@
       <c r="Q49" s="8"/>
       <c r="R49" s="9"/>
       <c r="S49" s="9"/>
-      <c r="T49" s="11"/>
+      <c r="T49" s="12"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="8"/>
@@ -1982,7 +2007,7 @@
       <c r="Q50" s="8"/>
       <c r="R50" s="9"/>
       <c r="S50" s="9"/>
-      <c r="T50" s="11"/>
+      <c r="T50" s="12"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="8"/>
@@ -2004,7 +2029,7 @@
       <c r="Q51" s="8"/>
       <c r="R51" s="9"/>
       <c r="S51" s="9"/>
-      <c r="T51" s="11"/>
+      <c r="T51" s="12"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="8"/>
@@ -2026,7 +2051,7 @@
       <c r="Q52" s="8"/>
       <c r="R52" s="9"/>
       <c r="S52" s="9"/>
-      <c r="T52" s="11"/>
+      <c r="T52" s="12"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="8"/>
@@ -2048,7 +2073,7 @@
       <c r="Q53" s="8"/>
       <c r="R53" s="9"/>
       <c r="S53" s="9"/>
-      <c r="T53" s="11"/>
+      <c r="T53" s="12"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="8"/>
@@ -2070,7 +2095,7 @@
       <c r="Q54" s="8"/>
       <c r="R54" s="9"/>
       <c r="S54" s="9"/>
-      <c r="T54" s="11"/>
+      <c r="T54" s="12"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="8"/>
@@ -2092,7 +2117,7 @@
       <c r="Q55" s="8"/>
       <c r="R55" s="9"/>
       <c r="S55" s="9"/>
-      <c r="T55" s="11"/>
+      <c r="T55" s="12"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="8"/>
@@ -2114,7 +2139,7 @@
       <c r="Q56" s="8"/>
       <c r="R56" s="9"/>
       <c r="S56" s="9"/>
-      <c r="T56" s="11"/>
+      <c r="T56" s="12"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="8"/>
@@ -2136,7 +2161,7 @@
       <c r="Q57" s="8"/>
       <c r="R57" s="9"/>
       <c r="S57" s="9"/>
-      <c r="T57" s="11"/>
+      <c r="T57" s="12"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="8"/>
@@ -2158,7 +2183,7 @@
       <c r="Q58" s="8"/>
       <c r="R58" s="9"/>
       <c r="S58" s="9"/>
-      <c r="T58" s="11"/>
+      <c r="T58" s="12"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="8"/>
@@ -2180,7 +2205,7 @@
       <c r="Q59" s="8"/>
       <c r="R59" s="9"/>
       <c r="S59" s="9"/>
-      <c r="T59" s="11"/>
+      <c r="T59" s="12"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="8"/>
@@ -2202,7 +2227,7 @@
       <c r="Q60" s="8"/>
       <c r="R60" s="9"/>
       <c r="S60" s="9"/>
-      <c r="T60" s="11"/>
+      <c r="T60" s="12"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="8"/>
@@ -2224,7 +2249,7 @@
       <c r="Q61" s="8"/>
       <c r="R61" s="9"/>
       <c r="S61" s="9"/>
-      <c r="T61" s="11"/>
+      <c r="T61" s="12"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="8"/>
@@ -2246,7 +2271,7 @@
       <c r="Q62" s="8"/>
       <c r="R62" s="9"/>
       <c r="S62" s="9"/>
-      <c r="T62" s="11"/>
+      <c r="T62" s="12"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="8"/>
@@ -2268,7 +2293,7 @@
       <c r="Q63" s="8"/>
       <c r="R63" s="9"/>
       <c r="S63" s="9"/>
-      <c r="T63" s="11"/>
+      <c r="T63" s="12"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="8"/>
@@ -2290,7 +2315,7 @@
       <c r="Q64" s="8"/>
       <c r="R64" s="9"/>
       <c r="S64" s="9"/>
-      <c r="T64" s="11"/>
+      <c r="T64" s="12"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="8"/>
@@ -2312,7 +2337,7 @@
       <c r="Q65" s="8"/>
       <c r="R65" s="9"/>
       <c r="S65" s="9"/>
-      <c r="T65" s="11"/>
+      <c r="T65" s="12"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="8"/>
@@ -2334,7 +2359,7 @@
       <c r="Q66" s="8"/>
       <c r="R66" s="9"/>
       <c r="S66" s="9"/>
-      <c r="T66" s="11"/>
+      <c r="T66" s="12"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="8"/>
@@ -2356,7 +2381,7 @@
       <c r="Q67" s="8"/>
       <c r="R67" s="9"/>
       <c r="S67" s="9"/>
-      <c r="T67" s="11"/>
+      <c r="T67" s="12"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="8"/>
@@ -2378,7 +2403,7 @@
       <c r="Q68" s="8"/>
       <c r="R68" s="9"/>
       <c r="S68" s="9"/>
-      <c r="T68" s="11"/>
+      <c r="T68" s="12"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="8"/>
@@ -2400,7 +2425,7 @@
       <c r="Q69" s="8"/>
       <c r="R69" s="9"/>
       <c r="S69" s="9"/>
-      <c r="T69" s="11"/>
+      <c r="T69" s="12"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="8"/>
@@ -2422,7 +2447,7 @@
       <c r="Q70" s="8"/>
       <c r="R70" s="9"/>
       <c r="S70" s="9"/>
-      <c r="T70" s="11"/>
+      <c r="T70" s="12"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="8"/>
@@ -2444,7 +2469,7 @@
       <c r="Q71" s="8"/>
       <c r="R71" s="9"/>
       <c r="S71" s="9"/>
-      <c r="T71" s="11"/>
+      <c r="T71" s="12"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="8"/>
@@ -2466,7 +2491,7 @@
       <c r="Q72" s="8"/>
       <c r="R72" s="9"/>
       <c r="S72" s="9"/>
-      <c r="T72" s="11"/>
+      <c r="T72" s="12"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="8"/>
@@ -2488,7 +2513,7 @@
       <c r="Q73" s="8"/>
       <c r="R73" s="9"/>
       <c r="S73" s="9"/>
-      <c r="T73" s="11"/>
+      <c r="T73" s="12"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="8"/>
@@ -2510,7 +2535,7 @@
       <c r="Q74" s="8"/>
       <c r="R74" s="9"/>
       <c r="S74" s="9"/>
-      <c r="T74" s="11"/>
+      <c r="T74" s="12"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="8"/>
@@ -2532,7 +2557,7 @@
       <c r="Q75" s="8"/>
       <c r="R75" s="9"/>
       <c r="S75" s="9"/>
-      <c r="T75" s="11"/>
+      <c r="T75" s="12"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="8"/>
@@ -2554,7 +2579,7 @@
       <c r="Q76" s="8"/>
       <c r="R76" s="9"/>
       <c r="S76" s="9"/>
-      <c r="T76" s="11"/>
+      <c r="T76" s="12"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="8"/>
@@ -2576,7 +2601,7 @@
       <c r="Q77" s="8"/>
       <c r="R77" s="9"/>
       <c r="S77" s="9"/>
-      <c r="T77" s="11"/>
+      <c r="T77" s="12"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="8"/>
@@ -2598,7 +2623,7 @@
       <c r="Q78" s="8"/>
       <c r="R78" s="9"/>
       <c r="S78" s="9"/>
-      <c r="T78" s="11"/>
+      <c r="T78" s="12"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="8"/>
@@ -2620,7 +2645,7 @@
       <c r="Q79" s="8"/>
       <c r="R79" s="9"/>
       <c r="S79" s="9"/>
-      <c r="T79" s="11"/>
+      <c r="T79" s="12"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="8"/>
@@ -2642,7 +2667,7 @@
       <c r="Q80" s="8"/>
       <c r="R80" s="9"/>
       <c r="S80" s="9"/>
-      <c r="T80" s="11"/>
+      <c r="T80" s="12"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="8"/>
@@ -2664,7 +2689,7 @@
       <c r="Q81" s="8"/>
       <c r="R81" s="9"/>
       <c r="S81" s="9"/>
-      <c r="T81" s="11"/>
+      <c r="T81" s="12"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="8"/>
@@ -2686,7 +2711,7 @@
       <c r="Q82" s="8"/>
       <c r="R82" s="9"/>
       <c r="S82" s="9"/>
-      <c r="T82" s="11"/>
+      <c r="T82" s="12"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="8"/>
@@ -2708,7 +2733,7 @@
       <c r="Q83" s="8"/>
       <c r="R83" s="9"/>
       <c r="S83" s="9"/>
-      <c r="T83" s="11"/>
+      <c r="T83" s="12"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="8"/>
@@ -2730,7 +2755,7 @@
       <c r="Q84" s="8"/>
       <c r="R84" s="9"/>
       <c r="S84" s="9"/>
-      <c r="T84" s="11"/>
+      <c r="T84" s="12"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="8"/>
@@ -2752,7 +2777,7 @@
       <c r="Q85" s="8"/>
       <c r="R85" s="9"/>
       <c r="S85" s="9"/>
-      <c r="T85" s="11"/>
+      <c r="T85" s="12"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="8"/>
@@ -2774,7 +2799,7 @@
       <c r="Q86" s="8"/>
       <c r="R86" s="9"/>
       <c r="S86" s="9"/>
-      <c r="T86" s="11"/>
+      <c r="T86" s="12"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="8"/>
@@ -2796,7 +2821,7 @@
       <c r="Q87" s="8"/>
       <c r="R87" s="9"/>
       <c r="S87" s="9"/>
-      <c r="T87" s="11"/>
+      <c r="T87" s="12"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="8"/>
@@ -2818,7 +2843,7 @@
       <c r="Q88" s="8"/>
       <c r="R88" s="9"/>
       <c r="S88" s="9"/>
-      <c r="T88" s="11"/>
+      <c r="T88" s="12"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="8"/>
@@ -2840,7 +2865,7 @@
       <c r="Q89" s="8"/>
       <c r="R89" s="9"/>
       <c r="S89" s="9"/>
-      <c r="T89" s="11"/>
+      <c r="T89" s="12"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="8"/>
@@ -2862,7 +2887,7 @@
       <c r="Q90" s="8"/>
       <c r="R90" s="9"/>
       <c r="S90" s="9"/>
-      <c r="T90" s="11"/>
+      <c r="T90" s="12"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="8"/>
@@ -2884,7 +2909,7 @@
       <c r="Q91" s="8"/>
       <c r="R91" s="9"/>
       <c r="S91" s="9"/>
-      <c r="T91" s="11"/>
+      <c r="T91" s="12"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="8"/>
@@ -2906,7 +2931,7 @@
       <c r="Q92" s="8"/>
       <c r="R92" s="9"/>
       <c r="S92" s="9"/>
-      <c r="T92" s="11"/>
+      <c r="T92" s="12"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="8"/>
@@ -2928,7 +2953,7 @@
       <c r="Q93" s="8"/>
       <c r="R93" s="9"/>
       <c r="S93" s="9"/>
-      <c r="T93" s="11"/>
+      <c r="T93" s="12"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="8"/>
@@ -2950,7 +2975,7 @@
       <c r="Q94" s="8"/>
       <c r="R94" s="9"/>
       <c r="S94" s="9"/>
-      <c r="T94" s="11"/>
+      <c r="T94" s="12"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="8"/>
@@ -2972,7 +2997,7 @@
       <c r="Q95" s="8"/>
       <c r="R95" s="9"/>
       <c r="S95" s="9"/>
-      <c r="T95" s="11"/>
+      <c r="T95" s="12"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="8"/>
@@ -2994,7 +3019,7 @@
       <c r="Q96" s="8"/>
       <c r="R96" s="9"/>
       <c r="S96" s="9"/>
-      <c r="T96" s="11"/>
+      <c r="T96" s="12"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="8"/>
@@ -3016,7 +3041,7 @@
       <c r="Q97" s="8"/>
       <c r="R97" s="9"/>
       <c r="S97" s="9"/>
-      <c r="T97" s="11"/>
+      <c r="T97" s="12"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="8"/>
@@ -3038,7 +3063,7 @@
       <c r="Q98" s="8"/>
       <c r="R98" s="9"/>
       <c r="S98" s="9"/>
-      <c r="T98" s="11"/>
+      <c r="T98" s="12"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="8"/>
@@ -3060,7 +3085,7 @@
       <c r="Q99" s="8"/>
       <c r="R99" s="9"/>
       <c r="S99" s="9"/>
-      <c r="T99" s="11"/>
+      <c r="T99" s="12"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="8"/>
@@ -3082,7 +3107,7 @@
       <c r="Q100" s="8"/>
       <c r="R100" s="9"/>
       <c r="S100" s="9"/>
-      <c r="T100" s="11"/>
+      <c r="T100" s="12"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="8"/>
@@ -3104,7 +3129,7 @@
       <c r="Q101" s="8"/>
       <c r="R101" s="9"/>
       <c r="S101" s="9"/>
-      <c r="T101" s="11"/>
+      <c r="T101" s="12"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="8"/>
@@ -3126,7 +3151,7 @@
       <c r="Q102" s="8"/>
       <c r="R102" s="9"/>
       <c r="S102" s="9"/>
-      <c r="T102" s="11"/>
+      <c r="T102" s="12"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="8"/>
@@ -3148,7 +3173,7 @@
       <c r="Q103" s="8"/>
       <c r="R103" s="9"/>
       <c r="S103" s="9"/>
-      <c r="T103" s="11"/>
+      <c r="T103" s="12"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="8"/>
@@ -3170,7 +3195,7 @@
       <c r="Q104" s="8"/>
       <c r="R104" s="9"/>
       <c r="S104" s="9"/>
-      <c r="T104" s="11"/>
+      <c r="T104" s="12"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="8"/>
@@ -3192,7 +3217,7 @@
       <c r="Q105" s="8"/>
       <c r="R105" s="9"/>
       <c r="S105" s="9"/>
-      <c r="T105" s="11"/>
+      <c r="T105" s="12"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="8"/>
@@ -3214,7 +3239,7 @@
       <c r="Q106" s="8"/>
       <c r="R106" s="9"/>
       <c r="S106" s="9"/>
-      <c r="T106" s="11"/>
+      <c r="T106" s="12"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="8"/>
@@ -3236,7 +3261,7 @@
       <c r="Q107" s="8"/>
       <c r="R107" s="9"/>
       <c r="S107" s="9"/>
-      <c r="T107" s="11"/>
+      <c r="T107" s="12"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="8"/>
@@ -3258,7 +3283,7 @@
       <c r="Q108" s="8"/>
       <c r="R108" s="9"/>
       <c r="S108" s="9"/>
-      <c r="T108" s="11"/>
+      <c r="T108" s="12"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="8"/>
@@ -3280,7 +3305,7 @@
       <c r="Q109" s="8"/>
       <c r="R109" s="9"/>
       <c r="S109" s="9"/>
-      <c r="T109" s="11"/>
+      <c r="T109" s="12"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="8"/>
@@ -3302,7 +3327,7 @@
       <c r="Q110" s="8"/>
       <c r="R110" s="9"/>
       <c r="S110" s="9"/>
-      <c r="T110" s="11"/>
+      <c r="T110" s="12"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="8"/>
@@ -3324,7 +3349,7 @@
       <c r="Q111" s="8"/>
       <c r="R111" s="9"/>
       <c r="S111" s="9"/>
-      <c r="T111" s="11"/>
+      <c r="T111" s="12"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="8"/>
@@ -3346,7 +3371,7 @@
       <c r="Q112" s="8"/>
       <c r="R112" s="9"/>
       <c r="S112" s="9"/>
-      <c r="T112" s="11"/>
+      <c r="T112" s="12"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="8"/>
@@ -3368,7 +3393,7 @@
       <c r="Q113" s="8"/>
       <c r="R113" s="9"/>
       <c r="S113" s="9"/>
-      <c r="T113" s="11"/>
+      <c r="T113" s="12"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="8"/>
@@ -3390,7 +3415,7 @@
       <c r="Q114" s="8"/>
       <c r="R114" s="9"/>
       <c r="S114" s="9"/>
-      <c r="T114" s="11"/>
+      <c r="T114" s="12"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="8"/>
@@ -3412,7 +3437,7 @@
       <c r="Q115" s="8"/>
       <c r="R115" s="9"/>
       <c r="S115" s="9"/>
-      <c r="T115" s="11"/>
+      <c r="T115" s="12"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="8"/>
@@ -3434,7 +3459,7 @@
       <c r="Q116" s="8"/>
       <c r="R116" s="9"/>
       <c r="S116" s="9"/>
-      <c r="T116" s="11"/>
+      <c r="T116" s="12"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="8"/>
@@ -3456,7 +3481,7 @@
       <c r="Q117" s="8"/>
       <c r="R117" s="9"/>
       <c r="S117" s="9"/>
-      <c r="T117" s="11"/>
+      <c r="T117" s="12"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="8"/>
@@ -3478,7 +3503,7 @@
       <c r="Q118" s="8"/>
       <c r="R118" s="9"/>
       <c r="S118" s="9"/>
-      <c r="T118" s="11"/>
+      <c r="T118" s="12"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="8"/>
@@ -3500,7 +3525,7 @@
       <c r="Q119" s="8"/>
       <c r="R119" s="9"/>
       <c r="S119" s="9"/>
-      <c r="T119" s="11"/>
+      <c r="T119" s="12"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="8"/>
@@ -3522,7 +3547,7 @@
       <c r="Q120" s="8"/>
       <c r="R120" s="9"/>
       <c r="S120" s="9"/>
-      <c r="T120" s="11"/>
+      <c r="T120" s="12"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="8"/>
@@ -3544,7 +3569,7 @@
       <c r="Q121" s="8"/>
       <c r="R121" s="9"/>
       <c r="S121" s="9"/>
-      <c r="T121" s="11"/>
+      <c r="T121" s="12"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="8"/>
@@ -3566,7 +3591,7 @@
       <c r="Q122" s="8"/>
       <c r="R122" s="9"/>
       <c r="S122" s="9"/>
-      <c r="T122" s="11"/>
+      <c r="T122" s="12"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="8"/>
@@ -3588,7 +3613,7 @@
       <c r="Q123" s="8"/>
       <c r="R123" s="9"/>
       <c r="S123" s="9"/>
-      <c r="T123" s="11"/>
+      <c r="T123" s="12"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="8"/>
@@ -3610,7 +3635,7 @@
       <c r="Q124" s="8"/>
       <c r="R124" s="9"/>
       <c r="S124" s="9"/>
-      <c r="T124" s="11"/>
+      <c r="T124" s="12"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="8"/>
@@ -3632,7 +3657,7 @@
       <c r="Q125" s="8"/>
       <c r="R125" s="9"/>
       <c r="S125" s="9"/>
-      <c r="T125" s="11"/>
+      <c r="T125" s="12"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="8"/>
@@ -3654,7 +3679,7 @@
       <c r="Q126" s="8"/>
       <c r="R126" s="9"/>
       <c r="S126" s="9"/>
-      <c r="T126" s="11"/>
+      <c r="T126" s="12"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="8"/>
@@ -3676,7 +3701,7 @@
       <c r="Q127" s="8"/>
       <c r="R127" s="9"/>
       <c r="S127" s="9"/>
-      <c r="T127" s="11"/>
+      <c r="T127" s="12"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="8"/>
@@ -3698,7 +3723,7 @@
       <c r="Q128" s="8"/>
       <c r="R128" s="9"/>
       <c r="S128" s="9"/>
-      <c r="T128" s="11"/>
+      <c r="T128" s="12"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="8"/>
@@ -3720,7 +3745,7 @@
       <c r="Q129" s="8"/>
       <c r="R129" s="9"/>
       <c r="S129" s="9"/>
-      <c r="T129" s="11"/>
+      <c r="T129" s="12"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="8"/>
@@ -3742,7 +3767,7 @@
       <c r="Q130" s="8"/>
       <c r="R130" s="9"/>
       <c r="S130" s="9"/>
-      <c r="T130" s="11"/>
+      <c r="T130" s="12"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="8"/>
@@ -3764,7 +3789,7 @@
       <c r="Q131" s="8"/>
       <c r="R131" s="9"/>
       <c r="S131" s="9"/>
-      <c r="T131" s="11"/>
+      <c r="T131" s="12"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="8"/>
@@ -3786,7 +3811,7 @@
       <c r="Q132" s="8"/>
       <c r="R132" s="9"/>
       <c r="S132" s="9"/>
-      <c r="T132" s="11"/>
+      <c r="T132" s="12"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="8"/>
@@ -3808,7 +3833,7 @@
       <c r="Q133" s="8"/>
       <c r="R133" s="9"/>
       <c r="S133" s="9"/>
-      <c r="T133" s="11"/>
+      <c r="T133" s="12"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="8"/>
@@ -3830,7 +3855,7 @@
       <c r="Q134" s="8"/>
       <c r="R134" s="9"/>
       <c r="S134" s="9"/>
-      <c r="T134" s="11"/>
+      <c r="T134" s="12"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="8"/>
@@ -3852,7 +3877,7 @@
       <c r="Q135" s="8"/>
       <c r="R135" s="9"/>
       <c r="S135" s="9"/>
-      <c r="T135" s="11"/>
+      <c r="T135" s="12"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="8"/>
@@ -3874,7 +3899,7 @@
       <c r="Q136" s="8"/>
       <c r="R136" s="9"/>
       <c r="S136" s="9"/>
-      <c r="T136" s="11"/>
+      <c r="T136" s="12"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="8"/>
@@ -3896,7 +3921,7 @@
       <c r="Q137" s="8"/>
       <c r="R137" s="9"/>
       <c r="S137" s="9"/>
-      <c r="T137" s="11"/>
+      <c r="T137" s="12"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="8"/>
@@ -3918,7 +3943,7 @@
       <c r="Q138" s="8"/>
       <c r="R138" s="9"/>
       <c r="S138" s="9"/>
-      <c r="T138" s="11"/>
+      <c r="T138" s="12"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="8"/>
@@ -3940,7 +3965,7 @@
       <c r="Q139" s="8"/>
       <c r="R139" s="9"/>
       <c r="S139" s="9"/>
-      <c r="T139" s="11"/>
+      <c r="T139" s="12"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="8"/>
@@ -3962,7 +3987,7 @@
       <c r="Q140" s="8"/>
       <c r="R140" s="9"/>
       <c r="S140" s="9"/>
-      <c r="T140" s="11"/>
+      <c r="T140" s="12"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="8"/>
@@ -3984,7 +4009,7 @@
       <c r="Q141" s="8"/>
       <c r="R141" s="9"/>
       <c r="S141" s="9"/>
-      <c r="T141" s="11"/>
+      <c r="T141" s="12"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="8"/>
@@ -4006,7 +4031,7 @@
       <c r="Q142" s="8"/>
       <c r="R142" s="9"/>
       <c r="S142" s="9"/>
-      <c r="T142" s="11"/>
+      <c r="T142" s="12"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="8"/>
@@ -4028,7 +4053,7 @@
       <c r="Q143" s="8"/>
       <c r="R143" s="9"/>
       <c r="S143" s="9"/>
-      <c r="T143" s="11"/>
+      <c r="T143" s="12"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="8"/>
@@ -4050,7 +4075,7 @@
       <c r="Q144" s="8"/>
       <c r="R144" s="9"/>
       <c r="S144" s="9"/>
-      <c r="T144" s="11"/>
+      <c r="T144" s="12"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="8"/>
@@ -4072,7 +4097,7 @@
       <c r="Q145" s="8"/>
       <c r="R145" s="9"/>
       <c r="S145" s="9"/>
-      <c r="T145" s="11"/>
+      <c r="T145" s="12"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="8"/>
@@ -4094,7 +4119,7 @@
       <c r="Q146" s="8"/>
       <c r="R146" s="9"/>
       <c r="S146" s="9"/>
-      <c r="T146" s="11"/>
+      <c r="T146" s="12"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="8"/>
@@ -4116,7 +4141,7 @@
       <c r="Q147" s="8"/>
       <c r="R147" s="9"/>
       <c r="S147" s="9"/>
-      <c r="T147" s="11"/>
+      <c r="T147" s="12"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="8"/>
@@ -4138,7 +4163,7 @@
       <c r="Q148" s="8"/>
       <c r="R148" s="9"/>
       <c r="S148" s="9"/>
-      <c r="T148" s="11"/>
+      <c r="T148" s="12"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="8"/>
@@ -4160,7 +4185,7 @@
       <c r="Q149" s="8"/>
       <c r="R149" s="9"/>
       <c r="S149" s="9"/>
-      <c r="T149" s="11"/>
+      <c r="T149" s="12"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="8"/>
@@ -4182,7 +4207,7 @@
       <c r="Q150" s="8"/>
       <c r="R150" s="9"/>
       <c r="S150" s="9"/>
-      <c r="T150" s="11"/>
+      <c r="T150" s="12"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="8"/>
@@ -4204,7 +4229,7 @@
       <c r="Q151" s="8"/>
       <c r="R151" s="9"/>
       <c r="S151" s="9"/>
-      <c r="T151" s="11"/>
+      <c r="T151" s="12"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="8"/>
@@ -4226,7 +4251,7 @@
       <c r="Q152" s="8"/>
       <c r="R152" s="9"/>
       <c r="S152" s="9"/>
-      <c r="T152" s="11"/>
+      <c r="T152" s="12"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="8"/>
@@ -4248,7 +4273,7 @@
       <c r="Q153" s="8"/>
       <c r="R153" s="9"/>
       <c r="S153" s="9"/>
-      <c r="T153" s="11"/>
+      <c r="T153" s="12"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="8"/>
@@ -4270,7 +4295,7 @@
       <c r="Q154" s="8"/>
       <c r="R154" s="9"/>
       <c r="S154" s="9"/>
-      <c r="T154" s="11"/>
+      <c r="T154" s="12"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="8"/>
@@ -4292,7 +4317,7 @@
       <c r="Q155" s="8"/>
       <c r="R155" s="9"/>
       <c r="S155" s="9"/>
-      <c r="T155" s="11"/>
+      <c r="T155" s="12"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="8"/>
@@ -4314,7 +4339,7 @@
       <c r="Q156" s="8"/>
       <c r="R156" s="9"/>
       <c r="S156" s="9"/>
-      <c r="T156" s="11"/>
+      <c r="T156" s="12"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="8"/>
@@ -4336,7 +4361,7 @@
       <c r="Q157" s="8"/>
       <c r="R157" s="9"/>
       <c r="S157" s="9"/>
-      <c r="T157" s="11"/>
+      <c r="T157" s="12"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="8"/>
@@ -4358,7 +4383,7 @@
       <c r="Q158" s="8"/>
       <c r="R158" s="9"/>
       <c r="S158" s="9"/>
-      <c r="T158" s="11"/>
+      <c r="T158" s="12"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="8"/>
@@ -4380,7 +4405,7 @@
       <c r="Q159" s="8"/>
       <c r="R159" s="9"/>
       <c r="S159" s="9"/>
-      <c r="T159" s="11"/>
+      <c r="T159" s="12"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="8"/>
@@ -4402,7 +4427,7 @@
       <c r="Q160" s="8"/>
       <c r="R160" s="9"/>
       <c r="S160" s="9"/>
-      <c r="T160" s="11"/>
+      <c r="T160" s="12"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="8"/>
@@ -4424,7 +4449,7 @@
       <c r="Q161" s="8"/>
       <c r="R161" s="9"/>
       <c r="S161" s="9"/>
-      <c r="T161" s="11"/>
+      <c r="T161" s="12"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="8"/>
@@ -4446,7 +4471,7 @@
       <c r="Q162" s="8"/>
       <c r="R162" s="9"/>
       <c r="S162" s="9"/>
-      <c r="T162" s="11"/>
+      <c r="T162" s="12"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="8"/>
@@ -4468,7 +4493,7 @@
       <c r="Q163" s="8"/>
       <c r="R163" s="9"/>
       <c r="S163" s="9"/>
-      <c r="T163" s="11"/>
+      <c r="T163" s="12"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="8"/>
@@ -4490,7 +4515,7 @@
       <c r="Q164" s="8"/>
       <c r="R164" s="9"/>
       <c r="S164" s="9"/>
-      <c r="T164" s="11"/>
+      <c r="T164" s="12"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="8"/>
@@ -4512,7 +4537,7 @@
       <c r="Q165" s="8"/>
       <c r="R165" s="9"/>
       <c r="S165" s="9"/>
-      <c r="T165" s="11"/>
+      <c r="T165" s="12"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="8"/>
@@ -4534,7 +4559,7 @@
       <c r="Q166" s="8"/>
       <c r="R166" s="9"/>
       <c r="S166" s="9"/>
-      <c r="T166" s="11"/>
+      <c r="T166" s="12"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="8"/>
@@ -4556,7 +4581,7 @@
       <c r="Q167" s="8"/>
       <c r="R167" s="9"/>
       <c r="S167" s="9"/>
-      <c r="T167" s="11"/>
+      <c r="T167" s="12"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="8"/>
@@ -4578,7 +4603,7 @@
       <c r="Q168" s="8"/>
       <c r="R168" s="9"/>
       <c r="S168" s="9"/>
-      <c r="T168" s="11"/>
+      <c r="T168" s="12"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="8"/>
@@ -4600,7 +4625,7 @@
       <c r="Q169" s="8"/>
       <c r="R169" s="9"/>
       <c r="S169" s="9"/>
-      <c r="T169" s="11"/>
+      <c r="T169" s="12"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="8"/>
@@ -4622,7 +4647,7 @@
       <c r="Q170" s="8"/>
       <c r="R170" s="9"/>
       <c r="S170" s="9"/>
-      <c r="T170" s="11"/>
+      <c r="T170" s="12"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="8"/>
@@ -4644,7 +4669,7 @@
       <c r="Q171" s="8"/>
       <c r="R171" s="9"/>
       <c r="S171" s="9"/>
-      <c r="T171" s="11"/>
+      <c r="T171" s="12"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="8"/>
@@ -4666,7 +4691,7 @@
       <c r="Q172" s="8"/>
       <c r="R172" s="9"/>
       <c r="S172" s="9"/>
-      <c r="T172" s="11"/>
+      <c r="T172" s="12"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="8"/>
@@ -4688,7 +4713,7 @@
       <c r="Q173" s="8"/>
       <c r="R173" s="9"/>
       <c r="S173" s="9"/>
-      <c r="T173" s="11"/>
+      <c r="T173" s="12"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="8"/>
@@ -4710,7 +4735,7 @@
       <c r="Q174" s="8"/>
       <c r="R174" s="9"/>
       <c r="S174" s="9"/>
-      <c r="T174" s="11"/>
+      <c r="T174" s="12"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="8"/>
@@ -4732,7 +4757,7 @@
       <c r="Q175" s="8"/>
       <c r="R175" s="9"/>
       <c r="S175" s="9"/>
-      <c r="T175" s="11"/>
+      <c r="T175" s="12"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="8"/>
@@ -4754,7 +4779,7 @@
       <c r="Q176" s="8"/>
       <c r="R176" s="9"/>
       <c r="S176" s="9"/>
-      <c r="T176" s="11"/>
+      <c r="T176" s="12"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="8"/>
@@ -4776,7 +4801,7 @@
       <c r="Q177" s="8"/>
       <c r="R177" s="9"/>
       <c r="S177" s="9"/>
-      <c r="T177" s="11"/>
+      <c r="T177" s="12"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="8"/>
@@ -4798,7 +4823,7 @@
       <c r="Q178" s="8"/>
       <c r="R178" s="9"/>
       <c r="S178" s="9"/>
-      <c r="T178" s="11"/>
+      <c r="T178" s="12"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="8"/>
@@ -4820,7 +4845,7 @@
       <c r="Q179" s="8"/>
       <c r="R179" s="9"/>
       <c r="S179" s="9"/>
-      <c r="T179" s="11"/>
+      <c r="T179" s="12"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="8"/>
@@ -4842,7 +4867,7 @@
       <c r="Q180" s="8"/>
       <c r="R180" s="9"/>
       <c r="S180" s="9"/>
-      <c r="T180" s="11"/>
+      <c r="T180" s="12"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="8"/>
@@ -4864,7 +4889,7 @@
       <c r="Q181" s="8"/>
       <c r="R181" s="9"/>
       <c r="S181" s="9"/>
-      <c r="T181" s="11"/>
+      <c r="T181" s="12"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="8"/>
@@ -4886,7 +4911,7 @@
       <c r="Q182" s="8"/>
       <c r="R182" s="9"/>
       <c r="S182" s="9"/>
-      <c r="T182" s="11"/>
+      <c r="T182" s="12"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="8"/>
@@ -4908,7 +4933,7 @@
       <c r="Q183" s="8"/>
       <c r="R183" s="9"/>
       <c r="S183" s="9"/>
-      <c r="T183" s="11"/>
+      <c r="T183" s="12"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="8"/>
@@ -4930,7 +4955,7 @@
       <c r="Q184" s="8"/>
       <c r="R184" s="9"/>
       <c r="S184" s="9"/>
-      <c r="T184" s="11"/>
+      <c r="T184" s="12"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="8"/>
@@ -4952,7 +4977,7 @@
       <c r="Q185" s="8"/>
       <c r="R185" s="9"/>
       <c r="S185" s="9"/>
-      <c r="T185" s="11"/>
+      <c r="T185" s="12"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="8"/>
@@ -4974,7 +4999,7 @@
       <c r="Q186" s="8"/>
       <c r="R186" s="9"/>
       <c r="S186" s="9"/>
-      <c r="T186" s="11"/>
+      <c r="T186" s="12"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="8"/>
@@ -4996,7 +5021,7 @@
       <c r="Q187" s="8"/>
       <c r="R187" s="9"/>
       <c r="S187" s="9"/>
-      <c r="T187" s="11"/>
+      <c r="T187" s="12"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="8"/>
@@ -5018,7 +5043,7 @@
       <c r="Q188" s="8"/>
       <c r="R188" s="9"/>
       <c r="S188" s="9"/>
-      <c r="T188" s="11"/>
+      <c r="T188" s="12"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="8"/>
@@ -5040,7 +5065,7 @@
       <c r="Q189" s="8"/>
       <c r="R189" s="9"/>
       <c r="S189" s="9"/>
-      <c r="T189" s="11"/>
+      <c r="T189" s="12"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="8"/>
@@ -5062,7 +5087,7 @@
       <c r="Q190" s="8"/>
       <c r="R190" s="9"/>
       <c r="S190" s="9"/>
-      <c r="T190" s="11"/>
+      <c r="T190" s="12"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="8"/>
@@ -5084,7 +5109,7 @@
       <c r="Q191" s="8"/>
       <c r="R191" s="9"/>
       <c r="S191" s="9"/>
-      <c r="T191" s="11"/>
+      <c r="T191" s="12"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="8"/>
@@ -5106,7 +5131,7 @@
       <c r="Q192" s="8"/>
       <c r="R192" s="9"/>
       <c r="S192" s="9"/>
-      <c r="T192" s="11"/>
+      <c r="T192" s="12"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="8"/>
@@ -5128,7 +5153,7 @@
       <c r="Q193" s="8"/>
       <c r="R193" s="9"/>
       <c r="S193" s="9"/>
-      <c r="T193" s="11"/>
+      <c r="T193" s="12"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="8"/>
@@ -5150,7 +5175,7 @@
       <c r="Q194" s="8"/>
       <c r="R194" s="9"/>
       <c r="S194" s="9"/>
-      <c r="T194" s="11"/>
+      <c r="T194" s="12"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="8"/>
@@ -5172,7 +5197,7 @@
       <c r="Q195" s="8"/>
       <c r="R195" s="9"/>
       <c r="S195" s="9"/>
-      <c r="T195" s="11"/>
+      <c r="T195" s="12"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="8"/>
@@ -5194,7 +5219,7 @@
       <c r="Q196" s="8"/>
       <c r="R196" s="9"/>
       <c r="S196" s="9"/>
-      <c r="T196" s="11"/>
+      <c r="T196" s="12"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="8"/>
@@ -5216,7 +5241,7 @@
       <c r="Q197" s="8"/>
       <c r="R197" s="9"/>
       <c r="S197" s="9"/>
-      <c r="T197" s="11"/>
+      <c r="T197" s="12"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="8"/>
@@ -5238,7 +5263,7 @@
       <c r="Q198" s="8"/>
       <c r="R198" s="9"/>
       <c r="S198" s="9"/>
-      <c r="T198" s="11"/>
+      <c r="T198" s="12"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="8"/>
@@ -5260,7 +5285,7 @@
       <c r="Q199" s="8"/>
       <c r="R199" s="9"/>
       <c r="S199" s="9"/>
-      <c r="T199" s="11"/>
+      <c r="T199" s="12"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="8"/>
@@ -5282,7 +5307,7 @@
       <c r="Q200" s="8"/>
       <c r="R200" s="9"/>
       <c r="S200" s="9"/>
-      <c r="T200" s="11"/>
+      <c r="T200" s="12"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="8"/>
@@ -5304,7 +5329,7 @@
       <c r="Q201" s="8"/>
       <c r="R201" s="9"/>
       <c r="S201" s="9"/>
-      <c r="T201" s="11"/>
+      <c r="T201" s="12"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="8"/>
@@ -5326,7 +5351,7 @@
       <c r="Q202" s="8"/>
       <c r="R202" s="9"/>
       <c r="S202" s="9"/>
-      <c r="T202" s="11"/>
+      <c r="T202" s="12"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="8"/>
@@ -5348,7 +5373,7 @@
       <c r="Q203" s="8"/>
       <c r="R203" s="9"/>
       <c r="S203" s="9"/>
-      <c r="T203" s="11"/>
+      <c r="T203" s="12"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="8"/>
@@ -5370,7 +5395,7 @@
       <c r="Q204" s="8"/>
       <c r="R204" s="9"/>
       <c r="S204" s="9"/>
-      <c r="T204" s="11"/>
+      <c r="T204" s="12"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="8"/>
@@ -5392,7 +5417,7 @@
       <c r="Q205" s="8"/>
       <c r="R205" s="9"/>
       <c r="S205" s="9"/>
-      <c r="T205" s="11"/>
+      <c r="T205" s="12"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="8"/>
@@ -5414,7 +5439,7 @@
       <c r="Q206" s="8"/>
       <c r="R206" s="9"/>
       <c r="S206" s="9"/>
-      <c r="T206" s="11"/>
+      <c r="T206" s="12"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="8"/>
@@ -5436,7 +5461,7 @@
       <c r="Q207" s="8"/>
       <c r="R207" s="9"/>
       <c r="S207" s="9"/>
-      <c r="T207" s="11"/>
+      <c r="T207" s="12"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="8"/>
@@ -5458,7 +5483,7 @@
       <c r="Q208" s="8"/>
       <c r="R208" s="9"/>
       <c r="S208" s="9"/>
-      <c r="T208" s="11"/>
+      <c r="T208" s="12"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="8"/>
@@ -5480,7 +5505,7 @@
       <c r="Q209" s="8"/>
       <c r="R209" s="9"/>
       <c r="S209" s="9"/>
-      <c r="T209" s="11"/>
+      <c r="T209" s="12"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="8"/>
@@ -5502,7 +5527,7 @@
       <c r="Q210" s="8"/>
       <c r="R210" s="9"/>
       <c r="S210" s="9"/>
-      <c r="T210" s="11"/>
+      <c r="T210" s="12"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="8"/>
@@ -5524,7 +5549,7 @@
       <c r="Q211" s="8"/>
       <c r="R211" s="9"/>
       <c r="S211" s="9"/>
-      <c r="T211" s="11"/>
+      <c r="T211" s="12"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="8"/>
@@ -5546,7 +5571,7 @@
       <c r="Q212" s="8"/>
       <c r="R212" s="9"/>
       <c r="S212" s="9"/>
-      <c r="T212" s="11"/>
+      <c r="T212" s="12"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="8"/>
@@ -5568,7 +5593,7 @@
       <c r="Q213" s="8"/>
       <c r="R213" s="9"/>
       <c r="S213" s="9"/>
-      <c r="T213" s="11"/>
+      <c r="T213" s="12"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="8"/>
@@ -5590,7 +5615,7 @@
       <c r="Q214" s="8"/>
       <c r="R214" s="9"/>
       <c r="S214" s="9"/>
-      <c r="T214" s="11"/>
+      <c r="T214" s="12"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="8"/>
@@ -5612,7 +5637,7 @@
       <c r="Q215" s="8"/>
       <c r="R215" s="9"/>
       <c r="S215" s="9"/>
-      <c r="T215" s="11"/>
+      <c r="T215" s="12"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="8"/>
@@ -5634,7 +5659,7 @@
       <c r="Q216" s="8"/>
       <c r="R216" s="9"/>
       <c r="S216" s="9"/>
-      <c r="T216" s="11"/>
+      <c r="T216" s="12"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="8"/>
@@ -5656,7 +5681,7 @@
       <c r="Q217" s="8"/>
       <c r="R217" s="9"/>
       <c r="S217" s="9"/>
-      <c r="T217" s="11"/>
+      <c r="T217" s="12"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="8"/>
@@ -5678,7 +5703,7 @@
       <c r="Q218" s="8"/>
       <c r="R218" s="9"/>
       <c r="S218" s="9"/>
-      <c r="T218" s="11"/>
+      <c r="T218" s="12"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="13"/>
@@ -5700,2350 +5725,2350 @@
       <c r="Q219" s="13"/>
       <c r="R219" s="14"/>
       <c r="S219" s="14"/>
-      <c r="T219" s="11"/>
+      <c r="T219" s="12"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="T220" s="11"/>
+      <c r="T220" s="12"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
-      <c r="T221" s="11"/>
+      <c r="T221" s="12"/>
     </row>
     <row r="222" ht="15.75" customHeight="1">
-      <c r="T222" s="11"/>
+      <c r="T222" s="12"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="T223" s="11"/>
+      <c r="T223" s="12"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
-      <c r="T224" s="11"/>
+      <c r="T224" s="12"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
-      <c r="T225" s="11"/>
+      <c r="T225" s="12"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
-      <c r="T226" s="11"/>
+      <c r="T226" s="12"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="T227" s="11"/>
+      <c r="T227" s="12"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
-      <c r="T228" s="11"/>
+      <c r="T228" s="12"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
-      <c r="T229" s="11"/>
+      <c r="T229" s="12"/>
     </row>
     <row r="230" ht="15.75" customHeight="1">
-      <c r="T230" s="11"/>
+      <c r="T230" s="12"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
-      <c r="T231" s="11"/>
+      <c r="T231" s="12"/>
     </row>
     <row r="232" ht="15.75" customHeight="1">
-      <c r="T232" s="11"/>
+      <c r="T232" s="12"/>
     </row>
     <row r="233" ht="15.75" customHeight="1">
-      <c r="T233" s="11"/>
+      <c r="T233" s="12"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
-      <c r="T234" s="11"/>
+      <c r="T234" s="12"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
-      <c r="T235" s="11"/>
+      <c r="T235" s="12"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
-      <c r="T236" s="11"/>
+      <c r="T236" s="12"/>
     </row>
     <row r="237" ht="15.75" customHeight="1">
-      <c r="T237" s="11"/>
+      <c r="T237" s="12"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
-      <c r="T238" s="11"/>
+      <c r="T238" s="12"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
-      <c r="T239" s="11"/>
+      <c r="T239" s="12"/>
     </row>
     <row r="240" ht="15.75" customHeight="1">
-      <c r="T240" s="11"/>
+      <c r="T240" s="12"/>
     </row>
     <row r="241" ht="15.75" customHeight="1">
-      <c r="T241" s="11"/>
+      <c r="T241" s="12"/>
     </row>
     <row r="242" ht="15.75" customHeight="1">
-      <c r="T242" s="11"/>
+      <c r="T242" s="12"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
-      <c r="T243" s="11"/>
+      <c r="T243" s="12"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
-      <c r="T244" s="11"/>
+      <c r="T244" s="12"/>
     </row>
     <row r="245" ht="15.75" customHeight="1">
-      <c r="T245" s="11"/>
+      <c r="T245" s="12"/>
     </row>
     <row r="246" ht="15.75" customHeight="1">
-      <c r="T246" s="11"/>
+      <c r="T246" s="12"/>
     </row>
     <row r="247" ht="15.75" customHeight="1">
-      <c r="T247" s="11"/>
+      <c r="T247" s="12"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
-      <c r="T248" s="11"/>
+      <c r="T248" s="12"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
-      <c r="T249" s="11"/>
+      <c r="T249" s="12"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
-      <c r="T250" s="11"/>
+      <c r="T250" s="12"/>
     </row>
     <row r="251" ht="15.75" customHeight="1">
-      <c r="T251" s="11"/>
+      <c r="T251" s="12"/>
     </row>
     <row r="252" ht="15.75" customHeight="1">
-      <c r="T252" s="11"/>
+      <c r="T252" s="12"/>
     </row>
     <row r="253" ht="15.75" customHeight="1">
-      <c r="T253" s="11"/>
+      <c r="T253" s="12"/>
     </row>
     <row r="254" ht="15.75" customHeight="1">
-      <c r="T254" s="11"/>
+      <c r="T254" s="12"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="T255" s="11"/>
+      <c r="T255" s="12"/>
     </row>
     <row r="256" ht="15.75" customHeight="1">
-      <c r="T256" s="11"/>
+      <c r="T256" s="12"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
-      <c r="T257" s="11"/>
+      <c r="T257" s="12"/>
     </row>
     <row r="258" ht="15.75" customHeight="1">
-      <c r="T258" s="11"/>
+      <c r="T258" s="12"/>
     </row>
     <row r="259" ht="15.75" customHeight="1">
-      <c r="T259" s="11"/>
+      <c r="T259" s="12"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
-      <c r="T260" s="11"/>
+      <c r="T260" s="12"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
-      <c r="T261" s="11"/>
+      <c r="T261" s="12"/>
     </row>
     <row r="262" ht="15.75" customHeight="1">
-      <c r="T262" s="11"/>
+      <c r="T262" s="12"/>
     </row>
     <row r="263" ht="15.75" customHeight="1">
-      <c r="T263" s="11"/>
+      <c r="T263" s="12"/>
     </row>
     <row r="264" ht="15.75" customHeight="1">
-      <c r="T264" s="11"/>
+      <c r="T264" s="12"/>
     </row>
     <row r="265" ht="15.75" customHeight="1">
-      <c r="T265" s="11"/>
+      <c r="T265" s="12"/>
     </row>
     <row r="266" ht="15.75" customHeight="1">
-      <c r="T266" s="11"/>
+      <c r="T266" s="12"/>
     </row>
     <row r="267" ht="15.75" customHeight="1">
-      <c r="T267" s="11"/>
+      <c r="T267" s="12"/>
     </row>
     <row r="268" ht="15.75" customHeight="1">
-      <c r="T268" s="11"/>
+      <c r="T268" s="12"/>
     </row>
     <row r="269" ht="15.75" customHeight="1">
-      <c r="T269" s="11"/>
+      <c r="T269" s="12"/>
     </row>
     <row r="270" ht="15.75" customHeight="1">
-      <c r="T270" s="11"/>
+      <c r="T270" s="12"/>
     </row>
     <row r="271" ht="15.75" customHeight="1">
-      <c r="T271" s="11"/>
+      <c r="T271" s="12"/>
     </row>
     <row r="272" ht="15.75" customHeight="1">
-      <c r="T272" s="11"/>
+      <c r="T272" s="12"/>
     </row>
     <row r="273" ht="15.75" customHeight="1">
-      <c r="T273" s="11"/>
+      <c r="T273" s="12"/>
     </row>
     <row r="274" ht="15.75" customHeight="1">
-      <c r="T274" s="11"/>
+      <c r="T274" s="12"/>
     </row>
     <row r="275" ht="15.75" customHeight="1">
-      <c r="T275" s="11"/>
+      <c r="T275" s="12"/>
     </row>
     <row r="276" ht="15.75" customHeight="1">
-      <c r="T276" s="11"/>
+      <c r="T276" s="12"/>
     </row>
     <row r="277" ht="15.75" customHeight="1">
-      <c r="T277" s="11"/>
+      <c r="T277" s="12"/>
     </row>
     <row r="278" ht="15.75" customHeight="1">
-      <c r="T278" s="11"/>
+      <c r="T278" s="12"/>
     </row>
     <row r="279" ht="15.75" customHeight="1">
-      <c r="T279" s="11"/>
+      <c r="T279" s="12"/>
     </row>
     <row r="280" ht="15.75" customHeight="1">
-      <c r="T280" s="11"/>
+      <c r="T280" s="12"/>
     </row>
     <row r="281" ht="15.75" customHeight="1">
-      <c r="T281" s="11"/>
+      <c r="T281" s="12"/>
     </row>
     <row r="282" ht="15.75" customHeight="1">
-      <c r="T282" s="11"/>
+      <c r="T282" s="12"/>
     </row>
     <row r="283" ht="15.75" customHeight="1">
-      <c r="T283" s="11"/>
+      <c r="T283" s="12"/>
     </row>
     <row r="284" ht="15.75" customHeight="1">
-      <c r="T284" s="11"/>
+      <c r="T284" s="12"/>
     </row>
     <row r="285" ht="15.75" customHeight="1">
-      <c r="T285" s="11"/>
+      <c r="T285" s="12"/>
     </row>
     <row r="286" ht="15.75" customHeight="1">
-      <c r="T286" s="11"/>
+      <c r="T286" s="12"/>
     </row>
     <row r="287" ht="15.75" customHeight="1">
-      <c r="T287" s="11"/>
+      <c r="T287" s="12"/>
     </row>
     <row r="288" ht="15.75" customHeight="1">
-      <c r="T288" s="11"/>
+      <c r="T288" s="12"/>
     </row>
     <row r="289" ht="15.75" customHeight="1">
-      <c r="T289" s="11"/>
+      <c r="T289" s="12"/>
     </row>
     <row r="290" ht="15.75" customHeight="1">
-      <c r="T290" s="11"/>
+      <c r="T290" s="12"/>
     </row>
     <row r="291" ht="15.75" customHeight="1">
-      <c r="T291" s="11"/>
+      <c r="T291" s="12"/>
     </row>
     <row r="292" ht="15.75" customHeight="1">
-      <c r="T292" s="11"/>
+      <c r="T292" s="12"/>
     </row>
     <row r="293" ht="15.75" customHeight="1">
-      <c r="T293" s="11"/>
+      <c r="T293" s="12"/>
     </row>
     <row r="294" ht="15.75" customHeight="1">
-      <c r="T294" s="11"/>
+      <c r="T294" s="12"/>
     </row>
     <row r="295" ht="15.75" customHeight="1">
-      <c r="T295" s="11"/>
+      <c r="T295" s="12"/>
     </row>
     <row r="296" ht="15.75" customHeight="1">
-      <c r="T296" s="11"/>
+      <c r="T296" s="12"/>
     </row>
     <row r="297" ht="15.75" customHeight="1">
-      <c r="T297" s="11"/>
+      <c r="T297" s="12"/>
     </row>
     <row r="298" ht="15.75" customHeight="1">
-      <c r="T298" s="11"/>
+      <c r="T298" s="12"/>
     </row>
     <row r="299" ht="15.75" customHeight="1">
-      <c r="T299" s="11"/>
+      <c r="T299" s="12"/>
     </row>
     <row r="300" ht="15.75" customHeight="1">
-      <c r="T300" s="11"/>
+      <c r="T300" s="12"/>
     </row>
     <row r="301" ht="15.75" customHeight="1">
-      <c r="T301" s="11"/>
+      <c r="T301" s="12"/>
     </row>
     <row r="302" ht="15.75" customHeight="1">
-      <c r="T302" s="11"/>
+      <c r="T302" s="12"/>
     </row>
     <row r="303" ht="15.75" customHeight="1">
-      <c r="T303" s="11"/>
+      <c r="T303" s="12"/>
     </row>
     <row r="304" ht="15.75" customHeight="1">
-      <c r="T304" s="11"/>
+      <c r="T304" s="12"/>
     </row>
     <row r="305" ht="15.75" customHeight="1">
-      <c r="T305" s="11"/>
+      <c r="T305" s="12"/>
     </row>
     <row r="306" ht="15.75" customHeight="1">
-      <c r="T306" s="11"/>
+      <c r="T306" s="12"/>
     </row>
     <row r="307" ht="15.75" customHeight="1">
-      <c r="T307" s="11"/>
+      <c r="T307" s="12"/>
     </row>
     <row r="308" ht="15.75" customHeight="1">
-      <c r="T308" s="11"/>
+      <c r="T308" s="12"/>
     </row>
     <row r="309" ht="15.75" customHeight="1">
-      <c r="T309" s="11"/>
+      <c r="T309" s="12"/>
     </row>
     <row r="310" ht="15.75" customHeight="1">
-      <c r="T310" s="11"/>
+      <c r="T310" s="12"/>
     </row>
     <row r="311" ht="15.75" customHeight="1">
-      <c r="T311" s="11"/>
+      <c r="T311" s="12"/>
     </row>
     <row r="312" ht="15.75" customHeight="1">
-      <c r="T312" s="11"/>
+      <c r="T312" s="12"/>
     </row>
     <row r="313" ht="15.75" customHeight="1">
-      <c r="T313" s="11"/>
+      <c r="T313" s="12"/>
     </row>
     <row r="314" ht="15.75" customHeight="1">
-      <c r="T314" s="11"/>
+      <c r="T314" s="12"/>
     </row>
     <row r="315" ht="15.75" customHeight="1">
-      <c r="T315" s="11"/>
+      <c r="T315" s="12"/>
     </row>
     <row r="316" ht="15.75" customHeight="1">
-      <c r="T316" s="11"/>
+      <c r="T316" s="12"/>
     </row>
     <row r="317" ht="15.75" customHeight="1">
-      <c r="T317" s="11"/>
+      <c r="T317" s="12"/>
     </row>
     <row r="318" ht="15.75" customHeight="1">
-      <c r="T318" s="11"/>
+      <c r="T318" s="12"/>
     </row>
     <row r="319" ht="15.75" customHeight="1">
-      <c r="T319" s="11"/>
+      <c r="T319" s="12"/>
     </row>
     <row r="320" ht="15.75" customHeight="1">
-      <c r="T320" s="11"/>
+      <c r="T320" s="12"/>
     </row>
     <row r="321" ht="15.75" customHeight="1">
-      <c r="T321" s="11"/>
+      <c r="T321" s="12"/>
     </row>
     <row r="322" ht="15.75" customHeight="1">
-      <c r="T322" s="11"/>
+      <c r="T322" s="12"/>
     </row>
     <row r="323" ht="15.75" customHeight="1">
-      <c r="T323" s="11"/>
+      <c r="T323" s="12"/>
     </row>
     <row r="324" ht="15.75" customHeight="1">
-      <c r="T324" s="11"/>
+      <c r="T324" s="12"/>
     </row>
     <row r="325" ht="15.75" customHeight="1">
-      <c r="T325" s="11"/>
+      <c r="T325" s="12"/>
     </row>
     <row r="326" ht="15.75" customHeight="1">
-      <c r="T326" s="11"/>
+      <c r="T326" s="12"/>
     </row>
     <row r="327" ht="15.75" customHeight="1">
-      <c r="T327" s="11"/>
+      <c r="T327" s="12"/>
     </row>
     <row r="328" ht="15.75" customHeight="1">
-      <c r="T328" s="11"/>
+      <c r="T328" s="12"/>
     </row>
     <row r="329" ht="15.75" customHeight="1">
-      <c r="T329" s="11"/>
+      <c r="T329" s="12"/>
     </row>
     <row r="330" ht="15.75" customHeight="1">
-      <c r="T330" s="11"/>
+      <c r="T330" s="12"/>
     </row>
     <row r="331" ht="15.75" customHeight="1">
-      <c r="T331" s="11"/>
+      <c r="T331" s="12"/>
     </row>
     <row r="332" ht="15.75" customHeight="1">
-      <c r="T332" s="11"/>
+      <c r="T332" s="12"/>
     </row>
     <row r="333" ht="15.75" customHeight="1">
-      <c r="T333" s="11"/>
+      <c r="T333" s="12"/>
     </row>
     <row r="334" ht="15.75" customHeight="1">
-      <c r="T334" s="11"/>
+      <c r="T334" s="12"/>
     </row>
     <row r="335" ht="15.75" customHeight="1">
-      <c r="T335" s="11"/>
+      <c r="T335" s="12"/>
     </row>
     <row r="336" ht="15.75" customHeight="1">
-      <c r="T336" s="11"/>
+      <c r="T336" s="12"/>
     </row>
     <row r="337" ht="15.75" customHeight="1">
-      <c r="T337" s="11"/>
+      <c r="T337" s="12"/>
     </row>
     <row r="338" ht="15.75" customHeight="1">
-      <c r="T338" s="11"/>
+      <c r="T338" s="12"/>
     </row>
     <row r="339" ht="15.75" customHeight="1">
-      <c r="T339" s="11"/>
+      <c r="T339" s="12"/>
     </row>
     <row r="340" ht="15.75" customHeight="1">
-      <c r="T340" s="11"/>
+      <c r="T340" s="12"/>
     </row>
     <row r="341" ht="15.75" customHeight="1">
-      <c r="T341" s="11"/>
+      <c r="T341" s="12"/>
     </row>
     <row r="342" ht="15.75" customHeight="1">
-      <c r="T342" s="11"/>
+      <c r="T342" s="12"/>
     </row>
     <row r="343" ht="15.75" customHeight="1">
-      <c r="T343" s="11"/>
+      <c r="T343" s="12"/>
     </row>
     <row r="344" ht="15.75" customHeight="1">
-      <c r="T344" s="11"/>
+      <c r="T344" s="12"/>
     </row>
     <row r="345" ht="15.75" customHeight="1">
-      <c r="T345" s="11"/>
+      <c r="T345" s="12"/>
     </row>
     <row r="346" ht="15.75" customHeight="1">
-      <c r="T346" s="11"/>
+      <c r="T346" s="12"/>
     </row>
     <row r="347" ht="15.75" customHeight="1">
-      <c r="T347" s="11"/>
+      <c r="T347" s="12"/>
     </row>
     <row r="348" ht="15.75" customHeight="1">
-      <c r="T348" s="11"/>
+      <c r="T348" s="12"/>
     </row>
     <row r="349" ht="15.75" customHeight="1">
-      <c r="T349" s="11"/>
+      <c r="T349" s="12"/>
     </row>
     <row r="350" ht="15.75" customHeight="1">
-      <c r="T350" s="11"/>
+      <c r="T350" s="12"/>
     </row>
     <row r="351" ht="15.75" customHeight="1">
-      <c r="T351" s="11"/>
+      <c r="T351" s="12"/>
     </row>
     <row r="352" ht="15.75" customHeight="1">
-      <c r="T352" s="11"/>
+      <c r="T352" s="12"/>
     </row>
     <row r="353" ht="15.75" customHeight="1">
-      <c r="T353" s="11"/>
+      <c r="T353" s="12"/>
     </row>
     <row r="354" ht="15.75" customHeight="1">
-      <c r="T354" s="11"/>
+      <c r="T354" s="12"/>
     </row>
     <row r="355" ht="15.75" customHeight="1">
-      <c r="T355" s="11"/>
+      <c r="T355" s="12"/>
     </row>
     <row r="356" ht="15.75" customHeight="1">
-      <c r="T356" s="11"/>
+      <c r="T356" s="12"/>
     </row>
     <row r="357" ht="15.75" customHeight="1">
-      <c r="T357" s="11"/>
+      <c r="T357" s="12"/>
     </row>
     <row r="358" ht="15.75" customHeight="1">
-      <c r="T358" s="11"/>
+      <c r="T358" s="12"/>
     </row>
     <row r="359" ht="15.75" customHeight="1">
-      <c r="T359" s="11"/>
+      <c r="T359" s="12"/>
     </row>
     <row r="360" ht="15.75" customHeight="1">
-      <c r="T360" s="11"/>
+      <c r="T360" s="12"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
-      <c r="T361" s="11"/>
+      <c r="T361" s="12"/>
     </row>
     <row r="362" ht="15.75" customHeight="1">
-      <c r="T362" s="11"/>
+      <c r="T362" s="12"/>
     </row>
     <row r="363" ht="15.75" customHeight="1">
-      <c r="T363" s="11"/>
+      <c r="T363" s="12"/>
     </row>
     <row r="364" ht="15.75" customHeight="1">
-      <c r="T364" s="11"/>
+      <c r="T364" s="12"/>
     </row>
     <row r="365" ht="15.75" customHeight="1">
-      <c r="T365" s="11"/>
+      <c r="T365" s="12"/>
     </row>
     <row r="366" ht="15.75" customHeight="1">
-      <c r="T366" s="11"/>
+      <c r="T366" s="12"/>
     </row>
     <row r="367" ht="15.75" customHeight="1">
-      <c r="T367" s="11"/>
+      <c r="T367" s="12"/>
     </row>
     <row r="368" ht="15.75" customHeight="1">
-      <c r="T368" s="11"/>
+      <c r="T368" s="12"/>
     </row>
     <row r="369" ht="15.75" customHeight="1">
-      <c r="T369" s="11"/>
+      <c r="T369" s="12"/>
     </row>
     <row r="370" ht="15.75" customHeight="1">
-      <c r="T370" s="11"/>
+      <c r="T370" s="12"/>
     </row>
     <row r="371" ht="15.75" customHeight="1">
-      <c r="T371" s="11"/>
+      <c r="T371" s="12"/>
     </row>
     <row r="372" ht="15.75" customHeight="1">
-      <c r="T372" s="11"/>
+      <c r="T372" s="12"/>
     </row>
     <row r="373" ht="15.75" customHeight="1">
-      <c r="T373" s="11"/>
+      <c r="T373" s="12"/>
     </row>
     <row r="374" ht="15.75" customHeight="1">
-      <c r="T374" s="11"/>
+      <c r="T374" s="12"/>
     </row>
     <row r="375" ht="15.75" customHeight="1">
-      <c r="T375" s="11"/>
+      <c r="T375" s="12"/>
     </row>
     <row r="376" ht="15.75" customHeight="1">
-      <c r="T376" s="11"/>
+      <c r="T376" s="12"/>
     </row>
     <row r="377" ht="15.75" customHeight="1">
-      <c r="T377" s="11"/>
+      <c r="T377" s="12"/>
     </row>
     <row r="378" ht="15.75" customHeight="1">
-      <c r="T378" s="11"/>
+      <c r="T378" s="12"/>
     </row>
     <row r="379" ht="15.75" customHeight="1">
-      <c r="T379" s="11"/>
+      <c r="T379" s="12"/>
     </row>
     <row r="380" ht="15.75" customHeight="1">
-      <c r="T380" s="11"/>
+      <c r="T380" s="12"/>
     </row>
     <row r="381" ht="15.75" customHeight="1">
-      <c r="T381" s="11"/>
+      <c r="T381" s="12"/>
     </row>
     <row r="382" ht="15.75" customHeight="1">
-      <c r="T382" s="11"/>
+      <c r="T382" s="12"/>
     </row>
     <row r="383" ht="15.75" customHeight="1">
-      <c r="T383" s="11"/>
+      <c r="T383" s="12"/>
     </row>
     <row r="384" ht="15.75" customHeight="1">
-      <c r="T384" s="11"/>
+      <c r="T384" s="12"/>
     </row>
     <row r="385" ht="15.75" customHeight="1">
-      <c r="T385" s="11"/>
+      <c r="T385" s="12"/>
     </row>
     <row r="386" ht="15.75" customHeight="1">
-      <c r="T386" s="11"/>
+      <c r="T386" s="12"/>
     </row>
     <row r="387" ht="15.75" customHeight="1">
-      <c r="T387" s="11"/>
+      <c r="T387" s="12"/>
     </row>
     <row r="388" ht="15.75" customHeight="1">
-      <c r="T388" s="11"/>
+      <c r="T388" s="12"/>
     </row>
     <row r="389" ht="15.75" customHeight="1">
-      <c r="T389" s="11"/>
+      <c r="T389" s="12"/>
     </row>
     <row r="390" ht="15.75" customHeight="1">
-      <c r="T390" s="11"/>
+      <c r="T390" s="12"/>
     </row>
     <row r="391" ht="15.75" customHeight="1">
-      <c r="T391" s="11"/>
+      <c r="T391" s="12"/>
     </row>
     <row r="392" ht="15.75" customHeight="1">
-      <c r="T392" s="11"/>
+      <c r="T392" s="12"/>
     </row>
     <row r="393" ht="15.75" customHeight="1">
-      <c r="T393" s="11"/>
+      <c r="T393" s="12"/>
     </row>
     <row r="394" ht="15.75" customHeight="1">
-      <c r="T394" s="11"/>
+      <c r="T394" s="12"/>
     </row>
     <row r="395" ht="15.75" customHeight="1">
-      <c r="T395" s="11"/>
+      <c r="T395" s="12"/>
     </row>
     <row r="396" ht="15.75" customHeight="1">
-      <c r="T396" s="11"/>
+      <c r="T396" s="12"/>
     </row>
     <row r="397" ht="15.75" customHeight="1">
-      <c r="T397" s="11"/>
+      <c r="T397" s="12"/>
     </row>
     <row r="398" ht="15.75" customHeight="1">
-      <c r="T398" s="11"/>
+      <c r="T398" s="12"/>
     </row>
     <row r="399" ht="15.75" customHeight="1">
-      <c r="T399" s="11"/>
+      <c r="T399" s="12"/>
     </row>
     <row r="400" ht="15.75" customHeight="1">
-      <c r="T400" s="11"/>
+      <c r="T400" s="12"/>
     </row>
     <row r="401" ht="15.75" customHeight="1">
-      <c r="T401" s="11"/>
+      <c r="T401" s="12"/>
     </row>
     <row r="402" ht="15.75" customHeight="1">
-      <c r="T402" s="11"/>
+      <c r="T402" s="12"/>
     </row>
     <row r="403" ht="15.75" customHeight="1">
-      <c r="T403" s="11"/>
+      <c r="T403" s="12"/>
     </row>
     <row r="404" ht="15.75" customHeight="1">
-      <c r="T404" s="11"/>
+      <c r="T404" s="12"/>
     </row>
     <row r="405" ht="15.75" customHeight="1">
-      <c r="T405" s="11"/>
+      <c r="T405" s="12"/>
     </row>
     <row r="406" ht="15.75" customHeight="1">
-      <c r="T406" s="11"/>
+      <c r="T406" s="12"/>
     </row>
     <row r="407" ht="15.75" customHeight="1">
-      <c r="T407" s="11"/>
+      <c r="T407" s="12"/>
     </row>
     <row r="408" ht="15.75" customHeight="1">
-      <c r="T408" s="11"/>
+      <c r="T408" s="12"/>
     </row>
     <row r="409" ht="15.75" customHeight="1">
-      <c r="T409" s="11"/>
+      <c r="T409" s="12"/>
     </row>
     <row r="410" ht="15.75" customHeight="1">
-      <c r="T410" s="11"/>
+      <c r="T410" s="12"/>
     </row>
     <row r="411" ht="15.75" customHeight="1">
-      <c r="T411" s="11"/>
+      <c r="T411" s="12"/>
     </row>
     <row r="412" ht="15.75" customHeight="1">
-      <c r="T412" s="11"/>
+      <c r="T412" s="12"/>
     </row>
     <row r="413" ht="15.75" customHeight="1">
-      <c r="T413" s="11"/>
+      <c r="T413" s="12"/>
     </row>
     <row r="414" ht="15.75" customHeight="1">
-      <c r="T414" s="11"/>
+      <c r="T414" s="12"/>
     </row>
     <row r="415" ht="15.75" customHeight="1">
-      <c r="T415" s="11"/>
+      <c r="T415" s="12"/>
     </row>
     <row r="416" ht="15.75" customHeight="1">
-      <c r="T416" s="11"/>
+      <c r="T416" s="12"/>
     </row>
     <row r="417" ht="15.75" customHeight="1">
-      <c r="T417" s="11"/>
+      <c r="T417" s="12"/>
     </row>
     <row r="418" ht="15.75" customHeight="1">
-      <c r="T418" s="11"/>
+      <c r="T418" s="12"/>
     </row>
     <row r="419" ht="15.75" customHeight="1">
-      <c r="T419" s="11"/>
+      <c r="T419" s="12"/>
     </row>
     <row r="420" ht="15.75" customHeight="1">
-      <c r="T420" s="11"/>
+      <c r="T420" s="12"/>
     </row>
     <row r="421" ht="15.75" customHeight="1">
-      <c r="T421" s="11"/>
+      <c r="T421" s="12"/>
     </row>
     <row r="422" ht="15.75" customHeight="1">
-      <c r="T422" s="11"/>
+      <c r="T422" s="12"/>
     </row>
     <row r="423" ht="15.75" customHeight="1">
-      <c r="T423" s="11"/>
+      <c r="T423" s="12"/>
     </row>
     <row r="424" ht="15.75" customHeight="1">
-      <c r="T424" s="11"/>
+      <c r="T424" s="12"/>
     </row>
     <row r="425" ht="15.75" customHeight="1">
-      <c r="T425" s="11"/>
+      <c r="T425" s="12"/>
     </row>
     <row r="426" ht="15.75" customHeight="1">
-      <c r="T426" s="11"/>
+      <c r="T426" s="12"/>
     </row>
     <row r="427" ht="15.75" customHeight="1">
-      <c r="T427" s="11"/>
+      <c r="T427" s="12"/>
     </row>
     <row r="428" ht="15.75" customHeight="1">
-      <c r="T428" s="11"/>
+      <c r="T428" s="12"/>
     </row>
     <row r="429" ht="15.75" customHeight="1">
-      <c r="T429" s="11"/>
+      <c r="T429" s="12"/>
     </row>
     <row r="430" ht="15.75" customHeight="1">
-      <c r="T430" s="11"/>
+      <c r="T430" s="12"/>
     </row>
     <row r="431" ht="15.75" customHeight="1">
-      <c r="T431" s="11"/>
+      <c r="T431" s="12"/>
     </row>
     <row r="432" ht="15.75" customHeight="1">
-      <c r="T432" s="11"/>
+      <c r="T432" s="12"/>
     </row>
     <row r="433" ht="15.75" customHeight="1">
-      <c r="T433" s="11"/>
+      <c r="T433" s="12"/>
     </row>
     <row r="434" ht="15.75" customHeight="1">
-      <c r="T434" s="11"/>
+      <c r="T434" s="12"/>
     </row>
     <row r="435" ht="15.75" customHeight="1">
-      <c r="T435" s="11"/>
+      <c r="T435" s="12"/>
     </row>
     <row r="436" ht="15.75" customHeight="1">
-      <c r="T436" s="11"/>
+      <c r="T436" s="12"/>
     </row>
     <row r="437" ht="15.75" customHeight="1">
-      <c r="T437" s="11"/>
+      <c r="T437" s="12"/>
     </row>
     <row r="438" ht="15.75" customHeight="1">
-      <c r="T438" s="11"/>
+      <c r="T438" s="12"/>
     </row>
     <row r="439" ht="15.75" customHeight="1">
-      <c r="T439" s="11"/>
+      <c r="T439" s="12"/>
     </row>
     <row r="440" ht="15.75" customHeight="1">
-      <c r="T440" s="11"/>
+      <c r="T440" s="12"/>
     </row>
     <row r="441" ht="15.75" customHeight="1">
-      <c r="T441" s="11"/>
+      <c r="T441" s="12"/>
     </row>
     <row r="442" ht="15.75" customHeight="1">
-      <c r="T442" s="11"/>
+      <c r="T442" s="12"/>
     </row>
     <row r="443" ht="15.75" customHeight="1">
-      <c r="T443" s="11"/>
+      <c r="T443" s="12"/>
     </row>
     <row r="444" ht="15.75" customHeight="1">
-      <c r="T444" s="11"/>
+      <c r="T444" s="12"/>
     </row>
     <row r="445" ht="15.75" customHeight="1">
-      <c r="T445" s="11"/>
+      <c r="T445" s="12"/>
     </row>
     <row r="446" ht="15.75" customHeight="1">
-      <c r="T446" s="11"/>
+      <c r="T446" s="12"/>
     </row>
     <row r="447" ht="15.75" customHeight="1">
-      <c r="T447" s="11"/>
+      <c r="T447" s="12"/>
     </row>
     <row r="448" ht="15.75" customHeight="1">
-      <c r="T448" s="11"/>
+      <c r="T448" s="12"/>
     </row>
     <row r="449" ht="15.75" customHeight="1">
-      <c r="T449" s="11"/>
+      <c r="T449" s="12"/>
     </row>
     <row r="450" ht="15.75" customHeight="1">
-      <c r="T450" s="11"/>
+      <c r="T450" s="12"/>
     </row>
     <row r="451" ht="15.75" customHeight="1">
-      <c r="T451" s="11"/>
+      <c r="T451" s="12"/>
     </row>
     <row r="452" ht="15.75" customHeight="1">
-      <c r="T452" s="11"/>
+      <c r="T452" s="12"/>
     </row>
     <row r="453" ht="15.75" customHeight="1">
-      <c r="T453" s="11"/>
+      <c r="T453" s="12"/>
     </row>
     <row r="454" ht="15.75" customHeight="1">
-      <c r="T454" s="11"/>
+      <c r="T454" s="12"/>
     </row>
     <row r="455" ht="15.75" customHeight="1">
-      <c r="T455" s="11"/>
+      <c r="T455" s="12"/>
     </row>
     <row r="456" ht="15.75" customHeight="1">
-      <c r="T456" s="11"/>
+      <c r="T456" s="12"/>
     </row>
     <row r="457" ht="15.75" customHeight="1">
-      <c r="T457" s="11"/>
+      <c r="T457" s="12"/>
     </row>
     <row r="458" ht="15.75" customHeight="1">
-      <c r="T458" s="11"/>
+      <c r="T458" s="12"/>
     </row>
     <row r="459" ht="15.75" customHeight="1">
-      <c r="T459" s="11"/>
+      <c r="T459" s="12"/>
     </row>
     <row r="460" ht="15.75" customHeight="1">
-      <c r="T460" s="11"/>
+      <c r="T460" s="12"/>
     </row>
     <row r="461" ht="15.75" customHeight="1">
-      <c r="T461" s="11"/>
+      <c r="T461" s="12"/>
     </row>
     <row r="462" ht="15.75" customHeight="1">
-      <c r="T462" s="11"/>
+      <c r="T462" s="12"/>
     </row>
     <row r="463" ht="15.75" customHeight="1">
-      <c r="T463" s="11"/>
+      <c r="T463" s="12"/>
     </row>
     <row r="464" ht="15.75" customHeight="1">
-      <c r="T464" s="11"/>
+      <c r="T464" s="12"/>
     </row>
     <row r="465" ht="15.75" customHeight="1">
-      <c r="T465" s="11"/>
+      <c r="T465" s="12"/>
     </row>
     <row r="466" ht="15.75" customHeight="1">
-      <c r="T466" s="11"/>
+      <c r="T466" s="12"/>
     </row>
     <row r="467" ht="15.75" customHeight="1">
-      <c r="T467" s="11"/>
+      <c r="T467" s="12"/>
     </row>
     <row r="468" ht="15.75" customHeight="1">
-      <c r="T468" s="11"/>
+      <c r="T468" s="12"/>
     </row>
     <row r="469" ht="15.75" customHeight="1">
-      <c r="T469" s="11"/>
+      <c r="T469" s="12"/>
     </row>
     <row r="470" ht="15.75" customHeight="1">
-      <c r="T470" s="11"/>
+      <c r="T470" s="12"/>
     </row>
     <row r="471" ht="15.75" customHeight="1">
-      <c r="T471" s="11"/>
+      <c r="T471" s="12"/>
     </row>
     <row r="472" ht="15.75" customHeight="1">
-      <c r="T472" s="11"/>
+      <c r="T472" s="12"/>
     </row>
     <row r="473" ht="15.75" customHeight="1">
-      <c r="T473" s="11"/>
+      <c r="T473" s="12"/>
     </row>
     <row r="474" ht="15.75" customHeight="1">
-      <c r="T474" s="11"/>
+      <c r="T474" s="12"/>
     </row>
     <row r="475" ht="15.75" customHeight="1">
-      <c r="T475" s="11"/>
+      <c r="T475" s="12"/>
     </row>
     <row r="476" ht="15.75" customHeight="1">
-      <c r="T476" s="11"/>
+      <c r="T476" s="12"/>
     </row>
     <row r="477" ht="15.75" customHeight="1">
-      <c r="T477" s="11"/>
+      <c r="T477" s="12"/>
     </row>
     <row r="478" ht="15.75" customHeight="1">
-      <c r="T478" s="11"/>
+      <c r="T478" s="12"/>
     </row>
     <row r="479" ht="15.75" customHeight="1">
-      <c r="T479" s="11"/>
+      <c r="T479" s="12"/>
     </row>
     <row r="480" ht="15.75" customHeight="1">
-      <c r="T480" s="11"/>
+      <c r="T480" s="12"/>
     </row>
     <row r="481" ht="15.75" customHeight="1">
-      <c r="T481" s="11"/>
+      <c r="T481" s="12"/>
     </row>
     <row r="482" ht="15.75" customHeight="1">
-      <c r="T482" s="11"/>
+      <c r="T482" s="12"/>
     </row>
     <row r="483" ht="15.75" customHeight="1">
-      <c r="T483" s="11"/>
+      <c r="T483" s="12"/>
     </row>
     <row r="484" ht="15.75" customHeight="1">
-      <c r="T484" s="11"/>
+      <c r="T484" s="12"/>
     </row>
     <row r="485" ht="15.75" customHeight="1">
-      <c r="T485" s="11"/>
+      <c r="T485" s="12"/>
     </row>
     <row r="486" ht="15.75" customHeight="1">
-      <c r="T486" s="11"/>
+      <c r="T486" s="12"/>
     </row>
     <row r="487" ht="15.75" customHeight="1">
-      <c r="T487" s="11"/>
+      <c r="T487" s="12"/>
     </row>
     <row r="488" ht="15.75" customHeight="1">
-      <c r="T488" s="11"/>
+      <c r="T488" s="12"/>
     </row>
     <row r="489" ht="15.75" customHeight="1">
-      <c r="T489" s="11"/>
+      <c r="T489" s="12"/>
     </row>
     <row r="490" ht="15.75" customHeight="1">
-      <c r="T490" s="11"/>
+      <c r="T490" s="12"/>
     </row>
     <row r="491" ht="15.75" customHeight="1">
-      <c r="T491" s="11"/>
+      <c r="T491" s="12"/>
     </row>
     <row r="492" ht="15.75" customHeight="1">
-      <c r="T492" s="11"/>
+      <c r="T492" s="12"/>
     </row>
     <row r="493" ht="15.75" customHeight="1">
-      <c r="T493" s="11"/>
+      <c r="T493" s="12"/>
     </row>
     <row r="494" ht="15.75" customHeight="1">
-      <c r="T494" s="11"/>
+      <c r="T494" s="12"/>
     </row>
     <row r="495" ht="15.75" customHeight="1">
-      <c r="T495" s="11"/>
+      <c r="T495" s="12"/>
     </row>
     <row r="496" ht="15.75" customHeight="1">
-      <c r="T496" s="11"/>
+      <c r="T496" s="12"/>
     </row>
     <row r="497" ht="15.75" customHeight="1">
-      <c r="T497" s="11"/>
+      <c r="T497" s="12"/>
     </row>
     <row r="498" ht="15.75" customHeight="1">
-      <c r="T498" s="11"/>
+      <c r="T498" s="12"/>
     </row>
     <row r="499" ht="15.75" customHeight="1">
-      <c r="T499" s="11"/>
+      <c r="T499" s="12"/>
     </row>
     <row r="500" ht="15.75" customHeight="1">
-      <c r="T500" s="11"/>
+      <c r="T500" s="12"/>
     </row>
     <row r="501" ht="15.75" customHeight="1">
-      <c r="T501" s="11"/>
+      <c r="T501" s="12"/>
     </row>
     <row r="502" ht="15.75" customHeight="1">
-      <c r="T502" s="11"/>
+      <c r="T502" s="12"/>
     </row>
     <row r="503" ht="15.75" customHeight="1">
-      <c r="T503" s="11"/>
+      <c r="T503" s="12"/>
     </row>
     <row r="504" ht="15.75" customHeight="1">
-      <c r="T504" s="11"/>
+      <c r="T504" s="12"/>
     </row>
     <row r="505" ht="15.75" customHeight="1">
-      <c r="T505" s="11"/>
+      <c r="T505" s="12"/>
     </row>
     <row r="506" ht="15.75" customHeight="1">
-      <c r="T506" s="11"/>
+      <c r="T506" s="12"/>
     </row>
     <row r="507" ht="15.75" customHeight="1">
-      <c r="T507" s="11"/>
+      <c r="T507" s="12"/>
     </row>
     <row r="508" ht="15.75" customHeight="1">
-      <c r="T508" s="11"/>
+      <c r="T508" s="12"/>
     </row>
     <row r="509" ht="15.75" customHeight="1">
-      <c r="T509" s="11"/>
+      <c r="T509" s="12"/>
     </row>
     <row r="510" ht="15.75" customHeight="1">
-      <c r="T510" s="11"/>
+      <c r="T510" s="12"/>
     </row>
     <row r="511" ht="15.75" customHeight="1">
-      <c r="T511" s="11"/>
+      <c r="T511" s="12"/>
     </row>
     <row r="512" ht="15.75" customHeight="1">
-      <c r="T512" s="11"/>
+      <c r="T512" s="12"/>
     </row>
     <row r="513" ht="15.75" customHeight="1">
-      <c r="T513" s="11"/>
+      <c r="T513" s="12"/>
     </row>
     <row r="514" ht="15.75" customHeight="1">
-      <c r="T514" s="11"/>
+      <c r="T514" s="12"/>
     </row>
     <row r="515" ht="15.75" customHeight="1">
-      <c r="T515" s="11"/>
+      <c r="T515" s="12"/>
     </row>
     <row r="516" ht="15.75" customHeight="1">
-      <c r="T516" s="11"/>
+      <c r="T516" s="12"/>
     </row>
     <row r="517" ht="15.75" customHeight="1">
-      <c r="T517" s="11"/>
+      <c r="T517" s="12"/>
     </row>
     <row r="518" ht="15.75" customHeight="1">
-      <c r="T518" s="11"/>
+      <c r="T518" s="12"/>
     </row>
     <row r="519" ht="15.75" customHeight="1">
-      <c r="T519" s="11"/>
+      <c r="T519" s="12"/>
     </row>
     <row r="520" ht="15.75" customHeight="1">
-      <c r="T520" s="11"/>
+      <c r="T520" s="12"/>
     </row>
     <row r="521" ht="15.75" customHeight="1">
-      <c r="T521" s="11"/>
+      <c r="T521" s="12"/>
     </row>
     <row r="522" ht="15.75" customHeight="1">
-      <c r="T522" s="11"/>
+      <c r="T522" s="12"/>
     </row>
     <row r="523" ht="15.75" customHeight="1">
-      <c r="T523" s="11"/>
+      <c r="T523" s="12"/>
     </row>
     <row r="524" ht="15.75" customHeight="1">
-      <c r="T524" s="11"/>
+      <c r="T524" s="12"/>
     </row>
     <row r="525" ht="15.75" customHeight="1">
-      <c r="T525" s="11"/>
+      <c r="T525" s="12"/>
     </row>
     <row r="526" ht="15.75" customHeight="1">
-      <c r="T526" s="11"/>
+      <c r="T526" s="12"/>
     </row>
     <row r="527" ht="15.75" customHeight="1">
-      <c r="T527" s="11"/>
+      <c r="T527" s="12"/>
     </row>
     <row r="528" ht="15.75" customHeight="1">
-      <c r="T528" s="11"/>
+      <c r="T528" s="12"/>
     </row>
     <row r="529" ht="15.75" customHeight="1">
-      <c r="T529" s="11"/>
+      <c r="T529" s="12"/>
     </row>
     <row r="530" ht="15.75" customHeight="1">
-      <c r="T530" s="11"/>
+      <c r="T530" s="12"/>
     </row>
     <row r="531" ht="15.75" customHeight="1">
-      <c r="T531" s="11"/>
+      <c r="T531" s="12"/>
     </row>
     <row r="532" ht="15.75" customHeight="1">
-      <c r="T532" s="11"/>
+      <c r="T532" s="12"/>
     </row>
     <row r="533" ht="15.75" customHeight="1">
-      <c r="T533" s="11"/>
+      <c r="T533" s="12"/>
     </row>
     <row r="534" ht="15.75" customHeight="1">
-      <c r="T534" s="11"/>
+      <c r="T534" s="12"/>
     </row>
     <row r="535" ht="15.75" customHeight="1">
-      <c r="T535" s="11"/>
+      <c r="T535" s="12"/>
     </row>
     <row r="536" ht="15.75" customHeight="1">
-      <c r="T536" s="11"/>
+      <c r="T536" s="12"/>
     </row>
     <row r="537" ht="15.75" customHeight="1">
-      <c r="T537" s="11"/>
+      <c r="T537" s="12"/>
     </row>
     <row r="538" ht="15.75" customHeight="1">
-      <c r="T538" s="11"/>
+      <c r="T538" s="12"/>
     </row>
     <row r="539" ht="15.75" customHeight="1">
-      <c r="T539" s="11"/>
+      <c r="T539" s="12"/>
     </row>
     <row r="540" ht="15.75" customHeight="1">
-      <c r="T540" s="11"/>
+      <c r="T540" s="12"/>
     </row>
     <row r="541" ht="15.75" customHeight="1">
-      <c r="T541" s="11"/>
+      <c r="T541" s="12"/>
     </row>
     <row r="542" ht="15.75" customHeight="1">
-      <c r="T542" s="11"/>
+      <c r="T542" s="12"/>
     </row>
     <row r="543" ht="15.75" customHeight="1">
-      <c r="T543" s="11"/>
+      <c r="T543" s="12"/>
     </row>
     <row r="544" ht="15.75" customHeight="1">
-      <c r="T544" s="11"/>
+      <c r="T544" s="12"/>
     </row>
     <row r="545" ht="15.75" customHeight="1">
-      <c r="T545" s="11"/>
+      <c r="T545" s="12"/>
     </row>
     <row r="546" ht="15.75" customHeight="1">
-      <c r="T546" s="11"/>
+      <c r="T546" s="12"/>
     </row>
     <row r="547" ht="15.75" customHeight="1">
-      <c r="T547" s="11"/>
+      <c r="T547" s="12"/>
     </row>
     <row r="548" ht="15.75" customHeight="1">
-      <c r="T548" s="11"/>
+      <c r="T548" s="12"/>
     </row>
     <row r="549" ht="15.75" customHeight="1">
-      <c r="T549" s="11"/>
+      <c r="T549" s="12"/>
     </row>
     <row r="550" ht="15.75" customHeight="1">
-      <c r="T550" s="11"/>
+      <c r="T550" s="12"/>
     </row>
     <row r="551" ht="15.75" customHeight="1">
-      <c r="T551" s="11"/>
+      <c r="T551" s="12"/>
     </row>
     <row r="552" ht="15.75" customHeight="1">
-      <c r="T552" s="11"/>
+      <c r="T552" s="12"/>
     </row>
     <row r="553" ht="15.75" customHeight="1">
-      <c r="T553" s="11"/>
+      <c r="T553" s="12"/>
     </row>
     <row r="554" ht="15.75" customHeight="1">
-      <c r="T554" s="11"/>
+      <c r="T554" s="12"/>
     </row>
     <row r="555" ht="15.75" customHeight="1">
-      <c r="T555" s="11"/>
+      <c r="T555" s="12"/>
     </row>
     <row r="556" ht="15.75" customHeight="1">
-      <c r="T556" s="11"/>
+      <c r="T556" s="12"/>
     </row>
     <row r="557" ht="15.75" customHeight="1">
-      <c r="T557" s="11"/>
+      <c r="T557" s="12"/>
     </row>
     <row r="558" ht="15.75" customHeight="1">
-      <c r="T558" s="11"/>
+      <c r="T558" s="12"/>
     </row>
     <row r="559" ht="15.75" customHeight="1">
-      <c r="T559" s="11"/>
+      <c r="T559" s="12"/>
     </row>
     <row r="560" ht="15.75" customHeight="1">
-      <c r="T560" s="11"/>
+      <c r="T560" s="12"/>
     </row>
     <row r="561" ht="15.75" customHeight="1">
-      <c r="T561" s="11"/>
+      <c r="T561" s="12"/>
     </row>
     <row r="562" ht="15.75" customHeight="1">
-      <c r="T562" s="11"/>
+      <c r="T562" s="12"/>
     </row>
     <row r="563" ht="15.75" customHeight="1">
-      <c r="T563" s="11"/>
+      <c r="T563" s="12"/>
     </row>
     <row r="564" ht="15.75" customHeight="1">
-      <c r="T564" s="11"/>
+      <c r="T564" s="12"/>
     </row>
     <row r="565" ht="15.75" customHeight="1">
-      <c r="T565" s="11"/>
+      <c r="T565" s="12"/>
     </row>
     <row r="566" ht="15.75" customHeight="1">
-      <c r="T566" s="11"/>
+      <c r="T566" s="12"/>
     </row>
     <row r="567" ht="15.75" customHeight="1">
-      <c r="T567" s="11"/>
+      <c r="T567" s="12"/>
     </row>
     <row r="568" ht="15.75" customHeight="1">
-      <c r="T568" s="11"/>
+      <c r="T568" s="12"/>
     </row>
     <row r="569" ht="15.75" customHeight="1">
-      <c r="T569" s="11"/>
+      <c r="T569" s="12"/>
     </row>
     <row r="570" ht="15.75" customHeight="1">
-      <c r="T570" s="11"/>
+      <c r="T570" s="12"/>
     </row>
     <row r="571" ht="15.75" customHeight="1">
-      <c r="T571" s="11"/>
+      <c r="T571" s="12"/>
     </row>
     <row r="572" ht="15.75" customHeight="1">
-      <c r="T572" s="11"/>
+      <c r="T572" s="12"/>
     </row>
     <row r="573" ht="15.75" customHeight="1">
-      <c r="T573" s="11"/>
+      <c r="T573" s="12"/>
     </row>
     <row r="574" ht="15.75" customHeight="1">
-      <c r="T574" s="11"/>
+      <c r="T574" s="12"/>
     </row>
     <row r="575" ht="15.75" customHeight="1">
-      <c r="T575" s="11"/>
+      <c r="T575" s="12"/>
     </row>
     <row r="576" ht="15.75" customHeight="1">
-      <c r="T576" s="11"/>
+      <c r="T576" s="12"/>
     </row>
     <row r="577" ht="15.75" customHeight="1">
-      <c r="T577" s="11"/>
+      <c r="T577" s="12"/>
     </row>
     <row r="578" ht="15.75" customHeight="1">
-      <c r="T578" s="11"/>
+      <c r="T578" s="12"/>
     </row>
     <row r="579" ht="15.75" customHeight="1">
-      <c r="T579" s="11"/>
+      <c r="T579" s="12"/>
     </row>
     <row r="580" ht="15.75" customHeight="1">
-      <c r="T580" s="11"/>
+      <c r="T580" s="12"/>
     </row>
     <row r="581" ht="15.75" customHeight="1">
-      <c r="T581" s="11"/>
+      <c r="T581" s="12"/>
     </row>
     <row r="582" ht="15.75" customHeight="1">
-      <c r="T582" s="11"/>
+      <c r="T582" s="12"/>
     </row>
     <row r="583" ht="15.75" customHeight="1">
-      <c r="T583" s="11"/>
+      <c r="T583" s="12"/>
     </row>
     <row r="584" ht="15.75" customHeight="1">
-      <c r="T584" s="11"/>
+      <c r="T584" s="12"/>
     </row>
     <row r="585" ht="15.75" customHeight="1">
-      <c r="T585" s="11"/>
+      <c r="T585" s="12"/>
     </row>
     <row r="586" ht="15.75" customHeight="1">
-      <c r="T586" s="11"/>
+      <c r="T586" s="12"/>
     </row>
     <row r="587" ht="15.75" customHeight="1">
-      <c r="T587" s="11"/>
+      <c r="T587" s="12"/>
     </row>
     <row r="588" ht="15.75" customHeight="1">
-      <c r="T588" s="11"/>
+      <c r="T588" s="12"/>
     </row>
     <row r="589" ht="15.75" customHeight="1">
-      <c r="T589" s="11"/>
+      <c r="T589" s="12"/>
     </row>
     <row r="590" ht="15.75" customHeight="1">
-      <c r="T590" s="11"/>
+      <c r="T590" s="12"/>
     </row>
     <row r="591" ht="15.75" customHeight="1">
-      <c r="T591" s="11"/>
+      <c r="T591" s="12"/>
     </row>
     <row r="592" ht="15.75" customHeight="1">
-      <c r="T592" s="11"/>
+      <c r="T592" s="12"/>
     </row>
     <row r="593" ht="15.75" customHeight="1">
-      <c r="T593" s="11"/>
+      <c r="T593" s="12"/>
     </row>
     <row r="594" ht="15.75" customHeight="1">
-      <c r="T594" s="11"/>
+      <c r="T594" s="12"/>
     </row>
     <row r="595" ht="15.75" customHeight="1">
-      <c r="T595" s="11"/>
+      <c r="T595" s="12"/>
     </row>
     <row r="596" ht="15.75" customHeight="1">
-      <c r="T596" s="11"/>
+      <c r="T596" s="12"/>
     </row>
     <row r="597" ht="15.75" customHeight="1">
-      <c r="T597" s="11"/>
+      <c r="T597" s="12"/>
     </row>
     <row r="598" ht="15.75" customHeight="1">
-      <c r="T598" s="11"/>
+      <c r="T598" s="12"/>
     </row>
     <row r="599" ht="15.75" customHeight="1">
-      <c r="T599" s="11"/>
+      <c r="T599" s="12"/>
     </row>
     <row r="600" ht="15.75" customHeight="1">
-      <c r="T600" s="11"/>
+      <c r="T600" s="12"/>
     </row>
     <row r="601" ht="15.75" customHeight="1">
-      <c r="T601" s="11"/>
+      <c r="T601" s="12"/>
     </row>
     <row r="602" ht="15.75" customHeight="1">
-      <c r="T602" s="11"/>
+      <c r="T602" s="12"/>
     </row>
     <row r="603" ht="15.75" customHeight="1">
-      <c r="T603" s="11"/>
+      <c r="T603" s="12"/>
     </row>
     <row r="604" ht="15.75" customHeight="1">
-      <c r="T604" s="11"/>
+      <c r="T604" s="12"/>
     </row>
     <row r="605" ht="15.75" customHeight="1">
-      <c r="T605" s="11"/>
+      <c r="T605" s="12"/>
     </row>
     <row r="606" ht="15.75" customHeight="1">
-      <c r="T606" s="11"/>
+      <c r="T606" s="12"/>
     </row>
     <row r="607" ht="15.75" customHeight="1">
-      <c r="T607" s="11"/>
+      <c r="T607" s="12"/>
     </row>
     <row r="608" ht="15.75" customHeight="1">
-      <c r="T608" s="11"/>
+      <c r="T608" s="12"/>
     </row>
     <row r="609" ht="15.75" customHeight="1">
-      <c r="T609" s="11"/>
+      <c r="T609" s="12"/>
     </row>
     <row r="610" ht="15.75" customHeight="1">
-      <c r="T610" s="11"/>
+      <c r="T610" s="12"/>
     </row>
     <row r="611" ht="15.75" customHeight="1">
-      <c r="T611" s="11"/>
+      <c r="T611" s="12"/>
     </row>
     <row r="612" ht="15.75" customHeight="1">
-      <c r="T612" s="11"/>
+      <c r="T612" s="12"/>
     </row>
     <row r="613" ht="15.75" customHeight="1">
-      <c r="T613" s="11"/>
+      <c r="T613" s="12"/>
     </row>
     <row r="614" ht="15.75" customHeight="1">
-      <c r="T614" s="11"/>
+      <c r="T614" s="12"/>
     </row>
     <row r="615" ht="15.75" customHeight="1">
-      <c r="T615" s="11"/>
+      <c r="T615" s="12"/>
     </row>
     <row r="616" ht="15.75" customHeight="1">
-      <c r="T616" s="11"/>
+      <c r="T616" s="12"/>
     </row>
     <row r="617" ht="15.75" customHeight="1">
-      <c r="T617" s="11"/>
+      <c r="T617" s="12"/>
     </row>
     <row r="618" ht="15.75" customHeight="1">
-      <c r="T618" s="11"/>
+      <c r="T618" s="12"/>
     </row>
     <row r="619" ht="15.75" customHeight="1">
-      <c r="T619" s="11"/>
+      <c r="T619" s="12"/>
     </row>
     <row r="620" ht="15.75" customHeight="1">
-      <c r="T620" s="11"/>
+      <c r="T620" s="12"/>
     </row>
     <row r="621" ht="15.75" customHeight="1">
-      <c r="T621" s="11"/>
+      <c r="T621" s="12"/>
     </row>
     <row r="622" ht="15.75" customHeight="1">
-      <c r="T622" s="11"/>
+      <c r="T622" s="12"/>
     </row>
     <row r="623" ht="15.75" customHeight="1">
-      <c r="T623" s="11"/>
+      <c r="T623" s="12"/>
     </row>
     <row r="624" ht="15.75" customHeight="1">
-      <c r="T624" s="11"/>
+      <c r="T624" s="12"/>
     </row>
     <row r="625" ht="15.75" customHeight="1">
-      <c r="T625" s="11"/>
+      <c r="T625" s="12"/>
     </row>
     <row r="626" ht="15.75" customHeight="1">
-      <c r="T626" s="11"/>
+      <c r="T626" s="12"/>
     </row>
     <row r="627" ht="15.75" customHeight="1">
-      <c r="T627" s="11"/>
+      <c r="T627" s="12"/>
     </row>
     <row r="628" ht="15.75" customHeight="1">
-      <c r="T628" s="11"/>
+      <c r="T628" s="12"/>
     </row>
     <row r="629" ht="15.75" customHeight="1">
-      <c r="T629" s="11"/>
+      <c r="T629" s="12"/>
     </row>
     <row r="630" ht="15.75" customHeight="1">
-      <c r="T630" s="11"/>
+      <c r="T630" s="12"/>
     </row>
     <row r="631" ht="15.75" customHeight="1">
-      <c r="T631" s="11"/>
+      <c r="T631" s="12"/>
     </row>
     <row r="632" ht="15.75" customHeight="1">
-      <c r="T632" s="11"/>
+      <c r="T632" s="12"/>
     </row>
     <row r="633" ht="15.75" customHeight="1">
-      <c r="T633" s="11"/>
+      <c r="T633" s="12"/>
     </row>
     <row r="634" ht="15.75" customHeight="1">
-      <c r="T634" s="11"/>
+      <c r="T634" s="12"/>
     </row>
     <row r="635" ht="15.75" customHeight="1">
-      <c r="T635" s="11"/>
+      <c r="T635" s="12"/>
     </row>
     <row r="636" ht="15.75" customHeight="1">
-      <c r="T636" s="11"/>
+      <c r="T636" s="12"/>
     </row>
     <row r="637" ht="15.75" customHeight="1">
-      <c r="T637" s="11"/>
+      <c r="T637" s="12"/>
     </row>
     <row r="638" ht="15.75" customHeight="1">
-      <c r="T638" s="11"/>
+      <c r="T638" s="12"/>
     </row>
     <row r="639" ht="15.75" customHeight="1">
-      <c r="T639" s="11"/>
+      <c r="T639" s="12"/>
     </row>
     <row r="640" ht="15.75" customHeight="1">
-      <c r="T640" s="11"/>
+      <c r="T640" s="12"/>
     </row>
     <row r="641" ht="15.75" customHeight="1">
-      <c r="T641" s="11"/>
+      <c r="T641" s="12"/>
     </row>
     <row r="642" ht="15.75" customHeight="1">
-      <c r="T642" s="11"/>
+      <c r="T642" s="12"/>
     </row>
     <row r="643" ht="15.75" customHeight="1">
-      <c r="T643" s="11"/>
+      <c r="T643" s="12"/>
     </row>
     <row r="644" ht="15.75" customHeight="1">
-      <c r="T644" s="11"/>
+      <c r="T644" s="12"/>
     </row>
     <row r="645" ht="15.75" customHeight="1">
-      <c r="T645" s="11"/>
+      <c r="T645" s="12"/>
     </row>
     <row r="646" ht="15.75" customHeight="1">
-      <c r="T646" s="11"/>
+      <c r="T646" s="12"/>
     </row>
     <row r="647" ht="15.75" customHeight="1">
-      <c r="T647" s="11"/>
+      <c r="T647" s="12"/>
     </row>
     <row r="648" ht="15.75" customHeight="1">
-      <c r="T648" s="11"/>
+      <c r="T648" s="12"/>
     </row>
     <row r="649" ht="15.75" customHeight="1">
-      <c r="T649" s="11"/>
+      <c r="T649" s="12"/>
     </row>
     <row r="650" ht="15.75" customHeight="1">
-      <c r="T650" s="11"/>
+      <c r="T650" s="12"/>
     </row>
     <row r="651" ht="15.75" customHeight="1">
-      <c r="T651" s="11"/>
+      <c r="T651" s="12"/>
     </row>
     <row r="652" ht="15.75" customHeight="1">
-      <c r="T652" s="11"/>
+      <c r="T652" s="12"/>
     </row>
     <row r="653" ht="15.75" customHeight="1">
-      <c r="T653" s="11"/>
+      <c r="T653" s="12"/>
     </row>
     <row r="654" ht="15.75" customHeight="1">
-      <c r="T654" s="11"/>
+      <c r="T654" s="12"/>
     </row>
     <row r="655" ht="15.75" customHeight="1">
-      <c r="T655" s="11"/>
+      <c r="T655" s="12"/>
     </row>
     <row r="656" ht="15.75" customHeight="1">
-      <c r="T656" s="11"/>
+      <c r="T656" s="12"/>
     </row>
     <row r="657" ht="15.75" customHeight="1">
-      <c r="T657" s="11"/>
+      <c r="T657" s="12"/>
     </row>
     <row r="658" ht="15.75" customHeight="1">
-      <c r="T658" s="11"/>
+      <c r="T658" s="12"/>
     </row>
     <row r="659" ht="15.75" customHeight="1">
-      <c r="T659" s="11"/>
+      <c r="T659" s="12"/>
     </row>
     <row r="660" ht="15.75" customHeight="1">
-      <c r="T660" s="11"/>
+      <c r="T660" s="12"/>
     </row>
     <row r="661" ht="15.75" customHeight="1">
-      <c r="T661" s="11"/>
+      <c r="T661" s="12"/>
     </row>
     <row r="662" ht="15.75" customHeight="1">
-      <c r="T662" s="11"/>
+      <c r="T662" s="12"/>
     </row>
     <row r="663" ht="15.75" customHeight="1">
-      <c r="T663" s="11"/>
+      <c r="T663" s="12"/>
     </row>
     <row r="664" ht="15.75" customHeight="1">
-      <c r="T664" s="11"/>
+      <c r="T664" s="12"/>
     </row>
     <row r="665" ht="15.75" customHeight="1">
-      <c r="T665" s="11"/>
+      <c r="T665" s="12"/>
     </row>
     <row r="666" ht="15.75" customHeight="1">
-      <c r="T666" s="11"/>
+      <c r="T666" s="12"/>
     </row>
     <row r="667" ht="15.75" customHeight="1">
-      <c r="T667" s="11"/>
+      <c r="T667" s="12"/>
     </row>
     <row r="668" ht="15.75" customHeight="1">
-      <c r="T668" s="11"/>
+      <c r="T668" s="12"/>
     </row>
     <row r="669" ht="15.75" customHeight="1">
-      <c r="T669" s="11"/>
+      <c r="T669" s="12"/>
     </row>
     <row r="670" ht="15.75" customHeight="1">
-      <c r="T670" s="11"/>
+      <c r="T670" s="12"/>
     </row>
     <row r="671" ht="15.75" customHeight="1">
-      <c r="T671" s="11"/>
+      <c r="T671" s="12"/>
     </row>
     <row r="672" ht="15.75" customHeight="1">
-      <c r="T672" s="11"/>
+      <c r="T672" s="12"/>
     </row>
     <row r="673" ht="15.75" customHeight="1">
-      <c r="T673" s="11"/>
+      <c r="T673" s="12"/>
     </row>
     <row r="674" ht="15.75" customHeight="1">
-      <c r="T674" s="11"/>
+      <c r="T674" s="12"/>
     </row>
     <row r="675" ht="15.75" customHeight="1">
-      <c r="T675" s="11"/>
+      <c r="T675" s="12"/>
     </row>
     <row r="676" ht="15.75" customHeight="1">
-      <c r="T676" s="11"/>
+      <c r="T676" s="12"/>
     </row>
     <row r="677" ht="15.75" customHeight="1">
-      <c r="T677" s="11"/>
+      <c r="T677" s="12"/>
     </row>
     <row r="678" ht="15.75" customHeight="1">
-      <c r="T678" s="11"/>
+      <c r="T678" s="12"/>
     </row>
     <row r="679" ht="15.75" customHeight="1">
-      <c r="T679" s="11"/>
+      <c r="T679" s="12"/>
     </row>
     <row r="680" ht="15.75" customHeight="1">
-      <c r="T680" s="11"/>
+      <c r="T680" s="12"/>
     </row>
     <row r="681" ht="15.75" customHeight="1">
-      <c r="T681" s="11"/>
+      <c r="T681" s="12"/>
     </row>
     <row r="682" ht="15.75" customHeight="1">
-      <c r="T682" s="11"/>
+      <c r="T682" s="12"/>
     </row>
     <row r="683" ht="15.75" customHeight="1">
-      <c r="T683" s="11"/>
+      <c r="T683" s="12"/>
     </row>
     <row r="684" ht="15.75" customHeight="1">
-      <c r="T684" s="11"/>
+      <c r="T684" s="12"/>
     </row>
     <row r="685" ht="15.75" customHeight="1">
-      <c r="T685" s="11"/>
+      <c r="T685" s="12"/>
     </row>
     <row r="686" ht="15.75" customHeight="1">
-      <c r="T686" s="11"/>
+      <c r="T686" s="12"/>
     </row>
     <row r="687" ht="15.75" customHeight="1">
-      <c r="T687" s="11"/>
+      <c r="T687" s="12"/>
     </row>
     <row r="688" ht="15.75" customHeight="1">
-      <c r="T688" s="11"/>
+      <c r="T688" s="12"/>
     </row>
     <row r="689" ht="15.75" customHeight="1">
-      <c r="T689" s="11"/>
+      <c r="T689" s="12"/>
     </row>
     <row r="690" ht="15.75" customHeight="1">
-      <c r="T690" s="11"/>
+      <c r="T690" s="12"/>
     </row>
     <row r="691" ht="15.75" customHeight="1">
-      <c r="T691" s="11"/>
+      <c r="T691" s="12"/>
     </row>
     <row r="692" ht="15.75" customHeight="1">
-      <c r="T692" s="11"/>
+      <c r="T692" s="12"/>
     </row>
     <row r="693" ht="15.75" customHeight="1">
-      <c r="T693" s="11"/>
+      <c r="T693" s="12"/>
     </row>
     <row r="694" ht="15.75" customHeight="1">
-      <c r="T694" s="11"/>
+      <c r="T694" s="12"/>
     </row>
     <row r="695" ht="15.75" customHeight="1">
-      <c r="T695" s="11"/>
+      <c r="T695" s="12"/>
     </row>
     <row r="696" ht="15.75" customHeight="1">
-      <c r="T696" s="11"/>
+      <c r="T696" s="12"/>
     </row>
     <row r="697" ht="15.75" customHeight="1">
-      <c r="T697" s="11"/>
+      <c r="T697" s="12"/>
     </row>
     <row r="698" ht="15.75" customHeight="1">
-      <c r="T698" s="11"/>
+      <c r="T698" s="12"/>
     </row>
     <row r="699" ht="15.75" customHeight="1">
-      <c r="T699" s="11"/>
+      <c r="T699" s="12"/>
     </row>
     <row r="700" ht="15.75" customHeight="1">
-      <c r="T700" s="11"/>
+      <c r="T700" s="12"/>
     </row>
     <row r="701" ht="15.75" customHeight="1">
-      <c r="T701" s="11"/>
+      <c r="T701" s="12"/>
     </row>
     <row r="702" ht="15.75" customHeight="1">
-      <c r="T702" s="11"/>
+      <c r="T702" s="12"/>
     </row>
     <row r="703" ht="15.75" customHeight="1">
-      <c r="T703" s="11"/>
+      <c r="T703" s="12"/>
     </row>
     <row r="704" ht="15.75" customHeight="1">
-      <c r="T704" s="11"/>
+      <c r="T704" s="12"/>
     </row>
     <row r="705" ht="15.75" customHeight="1">
-      <c r="T705" s="11"/>
+      <c r="T705" s="12"/>
     </row>
     <row r="706" ht="15.75" customHeight="1">
-      <c r="T706" s="11"/>
+      <c r="T706" s="12"/>
     </row>
     <row r="707" ht="15.75" customHeight="1">
-      <c r="T707" s="11"/>
+      <c r="T707" s="12"/>
     </row>
     <row r="708" ht="15.75" customHeight="1">
-      <c r="T708" s="11"/>
+      <c r="T708" s="12"/>
     </row>
     <row r="709" ht="15.75" customHeight="1">
-      <c r="T709" s="11"/>
+      <c r="T709" s="12"/>
     </row>
     <row r="710" ht="15.75" customHeight="1">
-      <c r="T710" s="11"/>
+      <c r="T710" s="12"/>
     </row>
     <row r="711" ht="15.75" customHeight="1">
-      <c r="T711" s="11"/>
+      <c r="T711" s="12"/>
     </row>
     <row r="712" ht="15.75" customHeight="1">
-      <c r="T712" s="11"/>
+      <c r="T712" s="12"/>
     </row>
     <row r="713" ht="15.75" customHeight="1">
-      <c r="T713" s="11"/>
+      <c r="T713" s="12"/>
     </row>
     <row r="714" ht="15.75" customHeight="1">
-      <c r="T714" s="11"/>
+      <c r="T714" s="12"/>
     </row>
     <row r="715" ht="15.75" customHeight="1">
-      <c r="T715" s="11"/>
+      <c r="T715" s="12"/>
     </row>
     <row r="716" ht="15.75" customHeight="1">
-      <c r="T716" s="11"/>
+      <c r="T716" s="12"/>
     </row>
     <row r="717" ht="15.75" customHeight="1">
-      <c r="T717" s="11"/>
+      <c r="T717" s="12"/>
     </row>
     <row r="718" ht="15.75" customHeight="1">
-      <c r="T718" s="11"/>
+      <c r="T718" s="12"/>
     </row>
     <row r="719" ht="15.75" customHeight="1">
-      <c r="T719" s="11"/>
+      <c r="T719" s="12"/>
     </row>
     <row r="720" ht="15.75" customHeight="1">
-      <c r="T720" s="11"/>
+      <c r="T720" s="12"/>
     </row>
     <row r="721" ht="15.75" customHeight="1">
-      <c r="T721" s="11"/>
+      <c r="T721" s="12"/>
     </row>
     <row r="722" ht="15.75" customHeight="1">
-      <c r="T722" s="11"/>
+      <c r="T722" s="12"/>
     </row>
     <row r="723" ht="15.75" customHeight="1">
-      <c r="T723" s="11"/>
+      <c r="T723" s="12"/>
     </row>
     <row r="724" ht="15.75" customHeight="1">
-      <c r="T724" s="11"/>
+      <c r="T724" s="12"/>
     </row>
     <row r="725" ht="15.75" customHeight="1">
-      <c r="T725" s="11"/>
+      <c r="T725" s="12"/>
     </row>
     <row r="726" ht="15.75" customHeight="1">
-      <c r="T726" s="11"/>
+      <c r="T726" s="12"/>
     </row>
     <row r="727" ht="15.75" customHeight="1">
-      <c r="T727" s="11"/>
+      <c r="T727" s="12"/>
     </row>
     <row r="728" ht="15.75" customHeight="1">
-      <c r="T728" s="11"/>
+      <c r="T728" s="12"/>
     </row>
     <row r="729" ht="15.75" customHeight="1">
-      <c r="T729" s="11"/>
+      <c r="T729" s="12"/>
     </row>
     <row r="730" ht="15.75" customHeight="1">
-      <c r="T730" s="11"/>
+      <c r="T730" s="12"/>
     </row>
     <row r="731" ht="15.75" customHeight="1">
-      <c r="T731" s="11"/>
+      <c r="T731" s="12"/>
     </row>
     <row r="732" ht="15.75" customHeight="1">
-      <c r="T732" s="11"/>
+      <c r="T732" s="12"/>
     </row>
     <row r="733" ht="15.75" customHeight="1">
-      <c r="T733" s="11"/>
+      <c r="T733" s="12"/>
     </row>
     <row r="734" ht="15.75" customHeight="1">
-      <c r="T734" s="11"/>
+      <c r="T734" s="12"/>
     </row>
     <row r="735" ht="15.75" customHeight="1">
-      <c r="T735" s="11"/>
+      <c r="T735" s="12"/>
     </row>
     <row r="736" ht="15.75" customHeight="1">
-      <c r="T736" s="11"/>
+      <c r="T736" s="12"/>
     </row>
     <row r="737" ht="15.75" customHeight="1">
-      <c r="T737" s="11"/>
+      <c r="T737" s="12"/>
     </row>
     <row r="738" ht="15.75" customHeight="1">
-      <c r="T738" s="11"/>
+      <c r="T738" s="12"/>
     </row>
     <row r="739" ht="15.75" customHeight="1">
-      <c r="T739" s="11"/>
+      <c r="T739" s="12"/>
     </row>
     <row r="740" ht="15.75" customHeight="1">
-      <c r="T740" s="11"/>
+      <c r="T740" s="12"/>
     </row>
     <row r="741" ht="15.75" customHeight="1">
-      <c r="T741" s="11"/>
+      <c r="T741" s="12"/>
     </row>
     <row r="742" ht="15.75" customHeight="1">
-      <c r="T742" s="11"/>
+      <c r="T742" s="12"/>
     </row>
     <row r="743" ht="15.75" customHeight="1">
-      <c r="T743" s="11"/>
+      <c r="T743" s="12"/>
     </row>
     <row r="744" ht="15.75" customHeight="1">
-      <c r="T744" s="11"/>
+      <c r="T744" s="12"/>
     </row>
     <row r="745" ht="15.75" customHeight="1">
-      <c r="T745" s="11"/>
+      <c r="T745" s="12"/>
     </row>
     <row r="746" ht="15.75" customHeight="1">
-      <c r="T746" s="11"/>
+      <c r="T746" s="12"/>
     </row>
     <row r="747" ht="15.75" customHeight="1">
-      <c r="T747" s="11"/>
+      <c r="T747" s="12"/>
     </row>
     <row r="748" ht="15.75" customHeight="1">
-      <c r="T748" s="11"/>
+      <c r="T748" s="12"/>
     </row>
     <row r="749" ht="15.75" customHeight="1">
-      <c r="T749" s="11"/>
+      <c r="T749" s="12"/>
     </row>
     <row r="750" ht="15.75" customHeight="1">
-      <c r="T750" s="11"/>
+      <c r="T750" s="12"/>
     </row>
     <row r="751" ht="15.75" customHeight="1">
-      <c r="T751" s="11"/>
+      <c r="T751" s="12"/>
     </row>
     <row r="752" ht="15.75" customHeight="1">
-      <c r="T752" s="11"/>
+      <c r="T752" s="12"/>
     </row>
     <row r="753" ht="15.75" customHeight="1">
-      <c r="T753" s="11"/>
+      <c r="T753" s="12"/>
     </row>
     <row r="754" ht="15.75" customHeight="1">
-      <c r="T754" s="11"/>
+      <c r="T754" s="12"/>
     </row>
     <row r="755" ht="15.75" customHeight="1">
-      <c r="T755" s="11"/>
+      <c r="T755" s="12"/>
     </row>
     <row r="756" ht="15.75" customHeight="1">
-      <c r="T756" s="11"/>
+      <c r="T756" s="12"/>
     </row>
     <row r="757" ht="15.75" customHeight="1">
-      <c r="T757" s="11"/>
+      <c r="T757" s="12"/>
     </row>
     <row r="758" ht="15.75" customHeight="1">
-      <c r="T758" s="11"/>
+      <c r="T758" s="12"/>
     </row>
     <row r="759" ht="15.75" customHeight="1">
-      <c r="T759" s="11"/>
+      <c r="T759" s="12"/>
     </row>
     <row r="760" ht="15.75" customHeight="1">
-      <c r="T760" s="11"/>
+      <c r="T760" s="12"/>
     </row>
     <row r="761" ht="15.75" customHeight="1">
-      <c r="T761" s="11"/>
+      <c r="T761" s="12"/>
     </row>
     <row r="762" ht="15.75" customHeight="1">
-      <c r="T762" s="11"/>
+      <c r="T762" s="12"/>
     </row>
     <row r="763" ht="15.75" customHeight="1">
-      <c r="T763" s="11"/>
+      <c r="T763" s="12"/>
     </row>
     <row r="764" ht="15.75" customHeight="1">
-      <c r="T764" s="11"/>
+      <c r="T764" s="12"/>
     </row>
     <row r="765" ht="15.75" customHeight="1">
-      <c r="T765" s="11"/>
+      <c r="T765" s="12"/>
     </row>
     <row r="766" ht="15.75" customHeight="1">
-      <c r="T766" s="11"/>
+      <c r="T766" s="12"/>
     </row>
     <row r="767" ht="15.75" customHeight="1">
-      <c r="T767" s="11"/>
+      <c r="T767" s="12"/>
     </row>
     <row r="768" ht="15.75" customHeight="1">
-      <c r="T768" s="11"/>
+      <c r="T768" s="12"/>
     </row>
     <row r="769" ht="15.75" customHeight="1">
-      <c r="T769" s="11"/>
+      <c r="T769" s="12"/>
     </row>
     <row r="770" ht="15.75" customHeight="1">
-      <c r="T770" s="11"/>
+      <c r="T770" s="12"/>
     </row>
     <row r="771" ht="15.75" customHeight="1">
-      <c r="T771" s="11"/>
+      <c r="T771" s="12"/>
     </row>
     <row r="772" ht="15.75" customHeight="1">
-      <c r="T772" s="11"/>
+      <c r="T772" s="12"/>
     </row>
     <row r="773" ht="15.75" customHeight="1">
-      <c r="T773" s="11"/>
+      <c r="T773" s="12"/>
     </row>
     <row r="774" ht="15.75" customHeight="1">
-      <c r="T774" s="11"/>
+      <c r="T774" s="12"/>
     </row>
     <row r="775" ht="15.75" customHeight="1">
-      <c r="T775" s="11"/>
+      <c r="T775" s="12"/>
     </row>
     <row r="776" ht="15.75" customHeight="1">
-      <c r="T776" s="11"/>
+      <c r="T776" s="12"/>
     </row>
     <row r="777" ht="15.75" customHeight="1">
-      <c r="T777" s="11"/>
+      <c r="T777" s="12"/>
     </row>
     <row r="778" ht="15.75" customHeight="1">
-      <c r="T778" s="11"/>
+      <c r="T778" s="12"/>
     </row>
     <row r="779" ht="15.75" customHeight="1">
-      <c r="T779" s="11"/>
+      <c r="T779" s="12"/>
     </row>
     <row r="780" ht="15.75" customHeight="1">
-      <c r="T780" s="11"/>
+      <c r="T780" s="12"/>
     </row>
     <row r="781" ht="15.75" customHeight="1">
-      <c r="T781" s="11"/>
+      <c r="T781" s="12"/>
     </row>
     <row r="782" ht="15.75" customHeight="1">
-      <c r="T782" s="11"/>
+      <c r="T782" s="12"/>
     </row>
     <row r="783" ht="15.75" customHeight="1">
-      <c r="T783" s="11"/>
+      <c r="T783" s="12"/>
     </row>
     <row r="784" ht="15.75" customHeight="1">
-      <c r="T784" s="11"/>
+      <c r="T784" s="12"/>
     </row>
     <row r="785" ht="15.75" customHeight="1">
-      <c r="T785" s="11"/>
+      <c r="T785" s="12"/>
     </row>
     <row r="786" ht="15.75" customHeight="1">
-      <c r="T786" s="11"/>
+      <c r="T786" s="12"/>
     </row>
     <row r="787" ht="15.75" customHeight="1">
-      <c r="T787" s="11"/>
+      <c r="T787" s="12"/>
     </row>
     <row r="788" ht="15.75" customHeight="1">
-      <c r="T788" s="11"/>
+      <c r="T788" s="12"/>
     </row>
     <row r="789" ht="15.75" customHeight="1">
-      <c r="T789" s="11"/>
+      <c r="T789" s="12"/>
     </row>
     <row r="790" ht="15.75" customHeight="1">
-      <c r="T790" s="11"/>
+      <c r="T790" s="12"/>
     </row>
     <row r="791" ht="15.75" customHeight="1">
-      <c r="T791" s="11"/>
+      <c r="T791" s="12"/>
     </row>
     <row r="792" ht="15.75" customHeight="1">
-      <c r="T792" s="11"/>
+      <c r="T792" s="12"/>
     </row>
     <row r="793" ht="15.75" customHeight="1">
-      <c r="T793" s="11"/>
+      <c r="T793" s="12"/>
     </row>
     <row r="794" ht="15.75" customHeight="1">
-      <c r="T794" s="11"/>
+      <c r="T794" s="12"/>
     </row>
     <row r="795" ht="15.75" customHeight="1">
-      <c r="T795" s="11"/>
+      <c r="T795" s="12"/>
     </row>
     <row r="796" ht="15.75" customHeight="1">
-      <c r="T796" s="11"/>
+      <c r="T796" s="12"/>
     </row>
     <row r="797" ht="15.75" customHeight="1">
-      <c r="T797" s="11"/>
+      <c r="T797" s="12"/>
     </row>
     <row r="798" ht="15.75" customHeight="1">
-      <c r="T798" s="11"/>
+      <c r="T798" s="12"/>
     </row>
     <row r="799" ht="15.75" customHeight="1">
-      <c r="T799" s="11"/>
+      <c r="T799" s="12"/>
     </row>
     <row r="800" ht="15.75" customHeight="1">
-      <c r="T800" s="11"/>
+      <c r="T800" s="12"/>
     </row>
     <row r="801" ht="15.75" customHeight="1">
-      <c r="T801" s="11"/>
+      <c r="T801" s="12"/>
     </row>
     <row r="802" ht="15.75" customHeight="1">
-      <c r="T802" s="11"/>
+      <c r="T802" s="12"/>
     </row>
     <row r="803" ht="15.75" customHeight="1">
-      <c r="T803" s="11"/>
+      <c r="T803" s="12"/>
     </row>
     <row r="804" ht="15.75" customHeight="1">
-      <c r="T804" s="11"/>
+      <c r="T804" s="12"/>
     </row>
     <row r="805" ht="15.75" customHeight="1">
-      <c r="T805" s="11"/>
+      <c r="T805" s="12"/>
     </row>
     <row r="806" ht="15.75" customHeight="1">
-      <c r="T806" s="11"/>
+      <c r="T806" s="12"/>
     </row>
     <row r="807" ht="15.75" customHeight="1">
-      <c r="T807" s="11"/>
+      <c r="T807" s="12"/>
     </row>
     <row r="808" ht="15.75" customHeight="1">
-      <c r="T808" s="11"/>
+      <c r="T808" s="12"/>
     </row>
     <row r="809" ht="15.75" customHeight="1">
-      <c r="T809" s="11"/>
+      <c r="T809" s="12"/>
     </row>
     <row r="810" ht="15.75" customHeight="1">
-      <c r="T810" s="11"/>
+      <c r="T810" s="12"/>
     </row>
     <row r="811" ht="15.75" customHeight="1">
-      <c r="T811" s="11"/>
+      <c r="T811" s="12"/>
     </row>
     <row r="812" ht="15.75" customHeight="1">
-      <c r="T812" s="11"/>
+      <c r="T812" s="12"/>
     </row>
     <row r="813" ht="15.75" customHeight="1">
-      <c r="T813" s="11"/>
+      <c r="T813" s="12"/>
     </row>
     <row r="814" ht="15.75" customHeight="1">
-      <c r="T814" s="11"/>
+      <c r="T814" s="12"/>
     </row>
     <row r="815" ht="15.75" customHeight="1">
-      <c r="T815" s="11"/>
+      <c r="T815" s="12"/>
     </row>
     <row r="816" ht="15.75" customHeight="1">
-      <c r="T816" s="11"/>
+      <c r="T816" s="12"/>
     </row>
     <row r="817" ht="15.75" customHeight="1">
-      <c r="T817" s="11"/>
+      <c r="T817" s="12"/>
     </row>
     <row r="818" ht="15.75" customHeight="1">
-      <c r="T818" s="11"/>
+      <c r="T818" s="12"/>
     </row>
     <row r="819" ht="15.75" customHeight="1">
-      <c r="T819" s="11"/>
+      <c r="T819" s="12"/>
     </row>
     <row r="820" ht="15.75" customHeight="1">
-      <c r="T820" s="11"/>
+      <c r="T820" s="12"/>
     </row>
     <row r="821" ht="15.75" customHeight="1">
-      <c r="T821" s="11"/>
+      <c r="T821" s="12"/>
     </row>
     <row r="822" ht="15.75" customHeight="1">
-      <c r="T822" s="11"/>
+      <c r="T822" s="12"/>
     </row>
     <row r="823" ht="15.75" customHeight="1">
-      <c r="T823" s="11"/>
+      <c r="T823" s="12"/>
     </row>
     <row r="824" ht="15.75" customHeight="1">
-      <c r="T824" s="11"/>
+      <c r="T824" s="12"/>
     </row>
     <row r="825" ht="15.75" customHeight="1">
-      <c r="T825" s="11"/>
+      <c r="T825" s="12"/>
     </row>
     <row r="826" ht="15.75" customHeight="1">
-      <c r="T826" s="11"/>
+      <c r="T826" s="12"/>
     </row>
     <row r="827" ht="15.75" customHeight="1">
-      <c r="T827" s="11"/>
+      <c r="T827" s="12"/>
     </row>
     <row r="828" ht="15.75" customHeight="1">
-      <c r="T828" s="11"/>
+      <c r="T828" s="12"/>
     </row>
     <row r="829" ht="15.75" customHeight="1">
-      <c r="T829" s="11"/>
+      <c r="T829" s="12"/>
     </row>
     <row r="830" ht="15.75" customHeight="1">
-      <c r="T830" s="11"/>
+      <c r="T830" s="12"/>
     </row>
     <row r="831" ht="15.75" customHeight="1">
-      <c r="T831" s="11"/>
+      <c r="T831" s="12"/>
     </row>
     <row r="832" ht="15.75" customHeight="1">
-      <c r="T832" s="11"/>
+      <c r="T832" s="12"/>
     </row>
     <row r="833" ht="15.75" customHeight="1">
-      <c r="T833" s="11"/>
+      <c r="T833" s="12"/>
     </row>
     <row r="834" ht="15.75" customHeight="1">
-      <c r="T834" s="11"/>
+      <c r="T834" s="12"/>
     </row>
     <row r="835" ht="15.75" customHeight="1">
-      <c r="T835" s="11"/>
+      <c r="T835" s="12"/>
     </row>
     <row r="836" ht="15.75" customHeight="1">
-      <c r="T836" s="11"/>
+      <c r="T836" s="12"/>
     </row>
     <row r="837" ht="15.75" customHeight="1">
-      <c r="T837" s="11"/>
+      <c r="T837" s="12"/>
     </row>
     <row r="838" ht="15.75" customHeight="1">
-      <c r="T838" s="11"/>
+      <c r="T838" s="12"/>
     </row>
     <row r="839" ht="15.75" customHeight="1">
-      <c r="T839" s="11"/>
+      <c r="T839" s="12"/>
     </row>
     <row r="840" ht="15.75" customHeight="1">
-      <c r="T840" s="11"/>
+      <c r="T840" s="12"/>
     </row>
     <row r="841" ht="15.75" customHeight="1">
-      <c r="T841" s="11"/>
+      <c r="T841" s="12"/>
     </row>
     <row r="842" ht="15.75" customHeight="1">
-      <c r="T842" s="11"/>
+      <c r="T842" s="12"/>
     </row>
     <row r="843" ht="15.75" customHeight="1">
-      <c r="T843" s="11"/>
+      <c r="T843" s="12"/>
     </row>
     <row r="844" ht="15.75" customHeight="1">
-      <c r="T844" s="11"/>
+      <c r="T844" s="12"/>
     </row>
     <row r="845" ht="15.75" customHeight="1">
-      <c r="T845" s="11"/>
+      <c r="T845" s="12"/>
     </row>
     <row r="846" ht="15.75" customHeight="1">
-      <c r="T846" s="11"/>
+      <c r="T846" s="12"/>
     </row>
     <row r="847" ht="15.75" customHeight="1">
-      <c r="T847" s="11"/>
+      <c r="T847" s="12"/>
     </row>
     <row r="848" ht="15.75" customHeight="1">
-      <c r="T848" s="11"/>
+      <c r="T848" s="12"/>
     </row>
     <row r="849" ht="15.75" customHeight="1">
-      <c r="T849" s="11"/>
+      <c r="T849" s="12"/>
     </row>
     <row r="850" ht="15.75" customHeight="1">
-      <c r="T850" s="11"/>
+      <c r="T850" s="12"/>
     </row>
     <row r="851" ht="15.75" customHeight="1">
-      <c r="T851" s="11"/>
+      <c r="T851" s="12"/>
     </row>
     <row r="852" ht="15.75" customHeight="1">
-      <c r="T852" s="11"/>
+      <c r="T852" s="12"/>
     </row>
     <row r="853" ht="15.75" customHeight="1">
-      <c r="T853" s="11"/>
+      <c r="T853" s="12"/>
     </row>
     <row r="854" ht="15.75" customHeight="1">
-      <c r="T854" s="11"/>
+      <c r="T854" s="12"/>
     </row>
     <row r="855" ht="15.75" customHeight="1">
-      <c r="T855" s="11"/>
+      <c r="T855" s="12"/>
     </row>
     <row r="856" ht="15.75" customHeight="1">
-      <c r="T856" s="11"/>
+      <c r="T856" s="12"/>
     </row>
     <row r="857" ht="15.75" customHeight="1">
-      <c r="T857" s="11"/>
+      <c r="T857" s="12"/>
     </row>
     <row r="858" ht="15.75" customHeight="1">
-      <c r="T858" s="11"/>
+      <c r="T858" s="12"/>
     </row>
     <row r="859" ht="15.75" customHeight="1">
-      <c r="T859" s="11"/>
+      <c r="T859" s="12"/>
     </row>
     <row r="860" ht="15.75" customHeight="1">
-      <c r="T860" s="11"/>
+      <c r="T860" s="12"/>
     </row>
     <row r="861" ht="15.75" customHeight="1">
-      <c r="T861" s="11"/>
+      <c r="T861" s="12"/>
     </row>
     <row r="862" ht="15.75" customHeight="1">
-      <c r="T862" s="11"/>
+      <c r="T862" s="12"/>
     </row>
     <row r="863" ht="15.75" customHeight="1">
-      <c r="T863" s="11"/>
+      <c r="T863" s="12"/>
     </row>
     <row r="864" ht="15.75" customHeight="1">
-      <c r="T864" s="11"/>
+      <c r="T864" s="12"/>
     </row>
     <row r="865" ht="15.75" customHeight="1">
-      <c r="T865" s="11"/>
+      <c r="T865" s="12"/>
     </row>
     <row r="866" ht="15.75" customHeight="1">
-      <c r="T866" s="11"/>
+      <c r="T866" s="12"/>
     </row>
     <row r="867" ht="15.75" customHeight="1">
-      <c r="T867" s="11"/>
+      <c r="T867" s="12"/>
     </row>
     <row r="868" ht="15.75" customHeight="1">
-      <c r="T868" s="11"/>
+      <c r="T868" s="12"/>
     </row>
     <row r="869" ht="15.75" customHeight="1">
-      <c r="T869" s="11"/>
+      <c r="T869" s="12"/>
     </row>
     <row r="870" ht="15.75" customHeight="1">
-      <c r="T870" s="11"/>
+      <c r="T870" s="12"/>
     </row>
     <row r="871" ht="15.75" customHeight="1">
-      <c r="T871" s="11"/>
+      <c r="T871" s="12"/>
     </row>
     <row r="872" ht="15.75" customHeight="1">
-      <c r="T872" s="11"/>
+      <c r="T872" s="12"/>
     </row>
     <row r="873" ht="15.75" customHeight="1">
-      <c r="T873" s="11"/>
+      <c r="T873" s="12"/>
     </row>
     <row r="874" ht="15.75" customHeight="1">
-      <c r="T874" s="11"/>
+      <c r="T874" s="12"/>
     </row>
     <row r="875" ht="15.75" customHeight="1">
-      <c r="T875" s="11"/>
+      <c r="T875" s="12"/>
     </row>
     <row r="876" ht="15.75" customHeight="1">
-      <c r="T876" s="11"/>
+      <c r="T876" s="12"/>
     </row>
     <row r="877" ht="15.75" customHeight="1">
-      <c r="T877" s="11"/>
+      <c r="T877" s="12"/>
     </row>
     <row r="878" ht="15.75" customHeight="1">
-      <c r="T878" s="11"/>
+      <c r="T878" s="12"/>
     </row>
     <row r="879" ht="15.75" customHeight="1">
-      <c r="T879" s="11"/>
+      <c r="T879" s="12"/>
     </row>
     <row r="880" ht="15.75" customHeight="1">
-      <c r="T880" s="11"/>
+      <c r="T880" s="12"/>
     </row>
     <row r="881" ht="15.75" customHeight="1">
-      <c r="T881" s="11"/>
+      <c r="T881" s="12"/>
     </row>
     <row r="882" ht="15.75" customHeight="1">
-      <c r="T882" s="11"/>
+      <c r="T882" s="12"/>
     </row>
     <row r="883" ht="15.75" customHeight="1">
-      <c r="T883" s="11"/>
+      <c r="T883" s="12"/>
     </row>
     <row r="884" ht="15.75" customHeight="1">
-      <c r="T884" s="11"/>
+      <c r="T884" s="12"/>
     </row>
     <row r="885" ht="15.75" customHeight="1">
-      <c r="T885" s="11"/>
+      <c r="T885" s="12"/>
     </row>
     <row r="886" ht="15.75" customHeight="1">
-      <c r="T886" s="11"/>
+      <c r="T886" s="12"/>
     </row>
     <row r="887" ht="15.75" customHeight="1">
-      <c r="T887" s="11"/>
+      <c r="T887" s="12"/>
     </row>
     <row r="888" ht="15.75" customHeight="1">
-      <c r="T888" s="11"/>
+      <c r="T888" s="12"/>
     </row>
     <row r="889" ht="15.75" customHeight="1">
-      <c r="T889" s="11"/>
+      <c r="T889" s="12"/>
     </row>
     <row r="890" ht="15.75" customHeight="1">
-      <c r="T890" s="11"/>
+      <c r="T890" s="12"/>
     </row>
     <row r="891" ht="15.75" customHeight="1">
-      <c r="T891" s="11"/>
+      <c r="T891" s="12"/>
     </row>
     <row r="892" ht="15.75" customHeight="1">
-      <c r="T892" s="11"/>
+      <c r="T892" s="12"/>
     </row>
     <row r="893" ht="15.75" customHeight="1">
-      <c r="T893" s="11"/>
+      <c r="T893" s="12"/>
     </row>
     <row r="894" ht="15.75" customHeight="1">
-      <c r="T894" s="11"/>
+      <c r="T894" s="12"/>
     </row>
     <row r="895" ht="15.75" customHeight="1">
-      <c r="T895" s="11"/>
+      <c r="T895" s="12"/>
     </row>
     <row r="896" ht="15.75" customHeight="1">
-      <c r="T896" s="11"/>
+      <c r="T896" s="12"/>
     </row>
     <row r="897" ht="15.75" customHeight="1">
-      <c r="T897" s="11"/>
+      <c r="T897" s="12"/>
     </row>
     <row r="898" ht="15.75" customHeight="1">
-      <c r="T898" s="11"/>
+      <c r="T898" s="12"/>
     </row>
     <row r="899" ht="15.75" customHeight="1">
-      <c r="T899" s="11"/>
+      <c r="T899" s="12"/>
     </row>
     <row r="900" ht="15.75" customHeight="1">
-      <c r="T900" s="11"/>
+      <c r="T900" s="12"/>
     </row>
     <row r="901" ht="15.75" customHeight="1">
-      <c r="T901" s="11"/>
+      <c r="T901" s="12"/>
     </row>
     <row r="902" ht="15.75" customHeight="1">
-      <c r="T902" s="11"/>
+      <c r="T902" s="12"/>
     </row>
     <row r="903" ht="15.75" customHeight="1">
-      <c r="T903" s="11"/>
+      <c r="T903" s="12"/>
     </row>
     <row r="904" ht="15.75" customHeight="1">
-      <c r="T904" s="11"/>
+      <c r="T904" s="12"/>
     </row>
     <row r="905" ht="15.75" customHeight="1">
-      <c r="T905" s="11"/>
+      <c r="T905" s="12"/>
     </row>
     <row r="906" ht="15.75" customHeight="1">
-      <c r="T906" s="11"/>
+      <c r="T906" s="12"/>
     </row>
     <row r="907" ht="15.75" customHeight="1">
-      <c r="T907" s="11"/>
+      <c r="T907" s="12"/>
     </row>
     <row r="908" ht="15.75" customHeight="1">
-      <c r="T908" s="11"/>
+      <c r="T908" s="12"/>
     </row>
     <row r="909" ht="15.75" customHeight="1">
-      <c r="T909" s="11"/>
+      <c r="T909" s="12"/>
     </row>
     <row r="910" ht="15.75" customHeight="1">
-      <c r="T910" s="11"/>
+      <c r="T910" s="12"/>
     </row>
     <row r="911" ht="15.75" customHeight="1">
-      <c r="T911" s="11"/>
+      <c r="T911" s="12"/>
     </row>
     <row r="912" ht="15.75" customHeight="1">
-      <c r="T912" s="11"/>
+      <c r="T912" s="12"/>
     </row>
     <row r="913" ht="15.75" customHeight="1">
-      <c r="T913" s="11"/>
+      <c r="T913" s="12"/>
     </row>
     <row r="914" ht="15.75" customHeight="1">
-      <c r="T914" s="11"/>
+      <c r="T914" s="12"/>
     </row>
     <row r="915" ht="15.75" customHeight="1">
-      <c r="T915" s="11"/>
+      <c r="T915" s="12"/>
     </row>
     <row r="916" ht="15.75" customHeight="1">
-      <c r="T916" s="11"/>
+      <c r="T916" s="12"/>
     </row>
     <row r="917" ht="15.75" customHeight="1">
-      <c r="T917" s="11"/>
+      <c r="T917" s="12"/>
     </row>
     <row r="918" ht="15.75" customHeight="1">
-      <c r="T918" s="11"/>
+      <c r="T918" s="12"/>
     </row>
     <row r="919" ht="15.75" customHeight="1">
-      <c r="T919" s="11"/>
+      <c r="T919" s="12"/>
     </row>
     <row r="920" ht="15.75" customHeight="1">
-      <c r="T920" s="11"/>
+      <c r="T920" s="12"/>
     </row>
     <row r="921" ht="15.75" customHeight="1">
-      <c r="T921" s="11"/>
+      <c r="T921" s="12"/>
     </row>
     <row r="922" ht="15.75" customHeight="1">
-      <c r="T922" s="11"/>
+      <c r="T922" s="12"/>
     </row>
     <row r="923" ht="15.75" customHeight="1">
-      <c r="T923" s="11"/>
+      <c r="T923" s="12"/>
     </row>
     <row r="924" ht="15.75" customHeight="1">
-      <c r="T924" s="11"/>
+      <c r="T924" s="12"/>
     </row>
     <row r="925" ht="15.75" customHeight="1">
-      <c r="T925" s="11"/>
+      <c r="T925" s="12"/>
     </row>
     <row r="926" ht="15.75" customHeight="1">
-      <c r="T926" s="11"/>
+      <c r="T926" s="12"/>
     </row>
     <row r="927" ht="15.75" customHeight="1">
-      <c r="T927" s="11"/>
+      <c r="T927" s="12"/>
     </row>
     <row r="928" ht="15.75" customHeight="1">
-      <c r="T928" s="11"/>
+      <c r="T928" s="12"/>
     </row>
     <row r="929" ht="15.75" customHeight="1">
-      <c r="T929" s="11"/>
+      <c r="T929" s="12"/>
     </row>
     <row r="930" ht="15.75" customHeight="1">
-      <c r="T930" s="11"/>
+      <c r="T930" s="12"/>
     </row>
     <row r="931" ht="15.75" customHeight="1">
-      <c r="T931" s="11"/>
+      <c r="T931" s="12"/>
     </row>
     <row r="932" ht="15.75" customHeight="1">
-      <c r="T932" s="11"/>
+      <c r="T932" s="12"/>
     </row>
     <row r="933" ht="15.75" customHeight="1">
-      <c r="T933" s="11"/>
+      <c r="T933" s="12"/>
     </row>
     <row r="934" ht="15.75" customHeight="1">
-      <c r="T934" s="11"/>
+      <c r="T934" s="12"/>
     </row>
     <row r="935" ht="15.75" customHeight="1">
-      <c r="T935" s="11"/>
+      <c r="T935" s="12"/>
     </row>
     <row r="936" ht="15.75" customHeight="1">
-      <c r="T936" s="11"/>
+      <c r="T936" s="12"/>
     </row>
     <row r="937" ht="15.75" customHeight="1">
-      <c r="T937" s="11"/>
+      <c r="T937" s="12"/>
     </row>
     <row r="938" ht="15.75" customHeight="1">
-      <c r="T938" s="11"/>
+      <c r="T938" s="12"/>
     </row>
     <row r="939" ht="15.75" customHeight="1">
-      <c r="T939" s="11"/>
+      <c r="T939" s="12"/>
     </row>
     <row r="940" ht="15.75" customHeight="1">
-      <c r="T940" s="11"/>
+      <c r="T940" s="12"/>
     </row>
     <row r="941" ht="15.75" customHeight="1">
-      <c r="T941" s="11"/>
+      <c r="T941" s="12"/>
     </row>
     <row r="942" ht="15.75" customHeight="1">
-      <c r="T942" s="11"/>
+      <c r="T942" s="12"/>
     </row>
     <row r="943" ht="15.75" customHeight="1">
-      <c r="T943" s="11"/>
+      <c r="T943" s="12"/>
     </row>
     <row r="944" ht="15.75" customHeight="1">
-      <c r="T944" s="11"/>
+      <c r="T944" s="12"/>
     </row>
     <row r="945" ht="15.75" customHeight="1">
-      <c r="T945" s="11"/>
+      <c r="T945" s="12"/>
     </row>
     <row r="946" ht="15.75" customHeight="1">
-      <c r="T946" s="11"/>
+      <c r="T946" s="12"/>
     </row>
     <row r="947" ht="15.75" customHeight="1">
-      <c r="T947" s="11"/>
+      <c r="T947" s="12"/>
     </row>
     <row r="948" ht="15.75" customHeight="1">
-      <c r="T948" s="11"/>
+      <c r="T948" s="12"/>
     </row>
     <row r="949" ht="15.75" customHeight="1">
-      <c r="T949" s="11"/>
+      <c r="T949" s="12"/>
     </row>
     <row r="950" ht="15.75" customHeight="1">
-      <c r="T950" s="11"/>
+      <c r="T950" s="12"/>
     </row>
     <row r="951" ht="15.75" customHeight="1">
-      <c r="T951" s="11"/>
+      <c r="T951" s="12"/>
     </row>
     <row r="952" ht="15.75" customHeight="1">
-      <c r="T952" s="11"/>
+      <c r="T952" s="12"/>
     </row>
     <row r="953" ht="15.75" customHeight="1">
-      <c r="T953" s="11"/>
+      <c r="T953" s="12"/>
     </row>
     <row r="954" ht="15.75" customHeight="1">
-      <c r="T954" s="11"/>
+      <c r="T954" s="12"/>
     </row>
     <row r="955" ht="15.75" customHeight="1">
-      <c r="T955" s="11"/>
+      <c r="T955" s="12"/>
     </row>
     <row r="956" ht="15.75" customHeight="1">
-      <c r="T956" s="11"/>
+      <c r="T956" s="12"/>
     </row>
     <row r="957" ht="15.75" customHeight="1">
-      <c r="T957" s="11"/>
+      <c r="T957" s="12"/>
     </row>
     <row r="958" ht="15.75" customHeight="1">
-      <c r="T958" s="11"/>
+      <c r="T958" s="12"/>
     </row>
     <row r="959" ht="15.75" customHeight="1">
-      <c r="T959" s="11"/>
+      <c r="T959" s="12"/>
     </row>
     <row r="960" ht="15.75" customHeight="1">
-      <c r="T960" s="11"/>
+      <c r="T960" s="12"/>
     </row>
     <row r="961" ht="15.75" customHeight="1">
-      <c r="T961" s="11"/>
+      <c r="T961" s="12"/>
     </row>
     <row r="962" ht="15.75" customHeight="1">
-      <c r="T962" s="11"/>
+      <c r="T962" s="12"/>
     </row>
     <row r="963" ht="15.75" customHeight="1">
-      <c r="T963" s="11"/>
+      <c r="T963" s="12"/>
     </row>
     <row r="964" ht="15.75" customHeight="1">
-      <c r="T964" s="11"/>
+      <c r="T964" s="12"/>
     </row>
     <row r="965" ht="15.75" customHeight="1">
-      <c r="T965" s="11"/>
+      <c r="T965" s="12"/>
     </row>
     <row r="966" ht="15.75" customHeight="1">
-      <c r="T966" s="11"/>
+      <c r="T966" s="12"/>
     </row>
     <row r="967" ht="15.75" customHeight="1">
-      <c r="T967" s="11"/>
+      <c r="T967" s="12"/>
     </row>
     <row r="968" ht="15.75" customHeight="1">
-      <c r="T968" s="11"/>
+      <c r="T968" s="12"/>
     </row>
     <row r="969" ht="15.75" customHeight="1">
-      <c r="T969" s="11"/>
+      <c r="T969" s="12"/>
     </row>
     <row r="970" ht="15.75" customHeight="1">
-      <c r="T970" s="11"/>
+      <c r="T970" s="12"/>
     </row>
     <row r="971" ht="15.75" customHeight="1">
-      <c r="T971" s="11"/>
+      <c r="T971" s="12"/>
     </row>
     <row r="972" ht="15.75" customHeight="1">
-      <c r="T972" s="11"/>
+      <c r="T972" s="12"/>
     </row>
     <row r="973" ht="15.75" customHeight="1">
-      <c r="T973" s="11"/>
+      <c r="T973" s="12"/>
     </row>
     <row r="974" ht="15.75" customHeight="1">
-      <c r="T974" s="11"/>
+      <c r="T974" s="12"/>
     </row>
     <row r="975" ht="15.75" customHeight="1">
-      <c r="T975" s="11"/>
+      <c r="T975" s="12"/>
     </row>
     <row r="976" ht="15.75" customHeight="1">
-      <c r="T976" s="11"/>
+      <c r="T976" s="12"/>
     </row>
     <row r="977" ht="15.75" customHeight="1">
-      <c r="T977" s="11"/>
+      <c r="T977" s="12"/>
     </row>
     <row r="978" ht="15.75" customHeight="1">
-      <c r="T978" s="11"/>
+      <c r="T978" s="12"/>
     </row>
     <row r="979" ht="15.75" customHeight="1">
-      <c r="T979" s="11"/>
+      <c r="T979" s="12"/>
     </row>
     <row r="980" ht="15.75" customHeight="1">
-      <c r="T980" s="11"/>
+      <c r="T980" s="12"/>
     </row>
     <row r="981" ht="15.75" customHeight="1">
-      <c r="T981" s="11"/>
+      <c r="T981" s="12"/>
     </row>
     <row r="982" ht="15.75" customHeight="1">
-      <c r="T982" s="11"/>
+      <c r="T982" s="12"/>
     </row>
     <row r="983" ht="15.75" customHeight="1">
-      <c r="T983" s="11"/>
+      <c r="T983" s="12"/>
     </row>
     <row r="984" ht="15.75" customHeight="1">
-      <c r="T984" s="11"/>
+      <c r="T984" s="12"/>
     </row>
     <row r="985" ht="15.75" customHeight="1">
-      <c r="T985" s="11"/>
+      <c r="T985" s="12"/>
     </row>
     <row r="986" ht="15.75" customHeight="1">
-      <c r="T986" s="11"/>
+      <c r="T986" s="12"/>
     </row>
     <row r="987" ht="15.75" customHeight="1">
-      <c r="T987" s="11"/>
+      <c r="T987" s="12"/>
     </row>
     <row r="988" ht="15.75" customHeight="1">
-      <c r="T988" s="11"/>
+      <c r="T988" s="12"/>
     </row>
     <row r="989" ht="15.75" customHeight="1">
-      <c r="T989" s="11"/>
+      <c r="T989" s="12"/>
     </row>
     <row r="990" ht="15.75" customHeight="1">
-      <c r="T990" s="11"/>
+      <c r="T990" s="12"/>
     </row>
     <row r="991" ht="15.75" customHeight="1">
-      <c r="T991" s="11"/>
+      <c r="T991" s="12"/>
     </row>
     <row r="992" ht="15.75" customHeight="1">
-      <c r="T992" s="11"/>
+      <c r="T992" s="12"/>
     </row>
     <row r="993" ht="15.75" customHeight="1">
-      <c r="T993" s="11"/>
+      <c r="T993" s="12"/>
     </row>
     <row r="994" ht="15.75" customHeight="1">
-      <c r="T994" s="11"/>
+      <c r="T994" s="12"/>
     </row>
     <row r="995" ht="15.75" customHeight="1">
-      <c r="T995" s="11"/>
+      <c r="T995" s="12"/>
     </row>
     <row r="996" ht="15.75" customHeight="1">
-      <c r="T996" s="11"/>
+      <c r="T996" s="12"/>
     </row>
     <row r="997" ht="15.75" customHeight="1">
-      <c r="T997" s="11"/>
+      <c r="T997" s="12"/>
     </row>
     <row r="998" ht="15.75" customHeight="1">
-      <c r="T998" s="11"/>
+      <c r="T998" s="12"/>
     </row>
     <row r="999" ht="15.75" customHeight="1">
-      <c r="T999" s="11"/>
+      <c r="T999" s="12"/>
     </row>
     <row r="1000" ht="15.75" customHeight="1">
-      <c r="T1000" s="11"/>
+      <c r="T1000" s="12"/>
     </row>
   </sheetData>
   <printOptions/>

--- a/JsonConverter/ExcelFiles/PetActiveSkillData.xlsx
+++ b/JsonConverter/ExcelFiles/PetActiveSkillData.xlsx
@@ -164,7 +164,7 @@
     <t>Fire</t>
   </si>
   <si>
-    <t>FramePawn/ActiveEffect</t>
+    <t>FramePawn_ActiveEffect</t>
   </si>
   <si>
     <t>pet_skill_water_001</t>
@@ -179,7 +179,7 @@
     <t>Cold</t>
   </si>
   <si>
-    <t>WaterPawn/ActiveEffect</t>
+    <t>WaterPawn_ActiveEffect</t>
   </si>
   <si>
     <t>pet_skill_earth_001</t>
@@ -197,7 +197,7 @@
     <t>Physical</t>
   </si>
   <si>
-    <t>EarthPawn/ActiveEffect</t>
+    <t>EarthPawn_ActiveEffect</t>
   </si>
   <si>
     <t>pet_skill_air_001</t>
@@ -209,7 +209,7 @@
     <t>관통하지 않는 빠른 바람 투사체를 발사해 단일 적에게 물리 피해를 줍니다. 기본 공격 자체는 상태이상을 부여하지 않습니다.</t>
   </si>
   <si>
-    <t>WindPawn/ActiveEffect</t>
+    <t>WindPawn_ActiveEffect</t>
   </si>
   <si>
     <t>pet_skill_taunt</t>
@@ -332,7 +332,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -367,10 +367,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
@@ -940,7 +943,7 @@
       <c r="L6" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="13" t="s">
         <v>59</v>
       </c>
       <c r="N6" s="8" t="s">
@@ -1042,7 +1045,7 @@
       <c r="L8" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="M8" s="11" t="s">
+      <c r="M8" s="13" t="s">
         <v>70</v>
       </c>
       <c r="N8" s="8"/>
@@ -1094,7 +1097,7 @@
       <c r="N9" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="O9" s="11" t="s">
+      <c r="O9" s="13" t="s">
         <v>78</v>
       </c>
       <c r="P9" s="8"/>
@@ -5706,25 +5709,25 @@
       <c r="T218" s="12"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
-      <c r="A219" s="13"/>
-      <c r="B219" s="13"/>
-      <c r="C219" s="13"/>
-      <c r="D219" s="14"/>
-      <c r="E219" s="13"/>
-      <c r="F219" s="13"/>
-      <c r="G219" s="14"/>
-      <c r="H219" s="13"/>
-      <c r="I219" s="13"/>
-      <c r="J219" s="13"/>
-      <c r="K219" s="15"/>
-      <c r="L219" s="13"/>
-      <c r="M219" s="13"/>
-      <c r="N219" s="13"/>
-      <c r="O219" s="13"/>
-      <c r="P219" s="13"/>
-      <c r="Q219" s="13"/>
-      <c r="R219" s="14"/>
-      <c r="S219" s="14"/>
+      <c r="A219" s="14"/>
+      <c r="B219" s="14"/>
+      <c r="C219" s="14"/>
+      <c r="D219" s="15"/>
+      <c r="E219" s="14"/>
+      <c r="F219" s="14"/>
+      <c r="G219" s="15"/>
+      <c r="H219" s="14"/>
+      <c r="I219" s="14"/>
+      <c r="J219" s="14"/>
+      <c r="K219" s="16"/>
+      <c r="L219" s="14"/>
+      <c r="M219" s="14"/>
+      <c r="N219" s="14"/>
+      <c r="O219" s="14"/>
+      <c r="P219" s="14"/>
+      <c r="Q219" s="14"/>
+      <c r="R219" s="15"/>
+      <c r="S219" s="15"/>
       <c r="T219" s="12"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
